--- a/baskets/Recap_baskets_EPS.xlsx
+++ b/baskets/Recap_baskets_EPS.xlsx
@@ -26,7 +26,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="9">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -62,11 +62,6 @@
     </font>
     <font>
       <name val="Arial"/>
-      <i val="1"/>
-      <color rgb="00C55A11"/>
-    </font>
-    <font>
-      <name val="Arial"/>
       <b val="1"/>
       <color rgb="00C00000"/>
       <sz val="9"/>
@@ -77,7 +72,7 @@
       <color rgb="007F7F7F"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -87,11 +82,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001F4E79"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FCE4D6"/>
       </patternFill>
     </fill>
     <fill>
@@ -131,7 +121,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -147,20 +137,17 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -528,7 +515,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:E31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -536,7 +523,6 @@
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="26" customWidth="1" min="4" max="4"/>
     <col width="26" customWidth="1" min="5" max="5"/>
-    <col width="48" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -549,7 +535,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Case orange = paire inventée (reprise d'une autre paire de la liste)  ·  Case grise = dispensé</t>
+          <t>Case grise = dispensé</t>
         </is>
       </c>
     </row>
@@ -577,11 +563,6 @@
       <c r="E4" s="3" t="inlineStr">
         <is>
           <t>Baskets extérieur</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>Remarque</t>
         </is>
       </c>
     </row>
@@ -604,42 +585,36 @@
           <t>Kiprun bleu</t>
         </is>
       </c>
-      <c r="E5" s="7" t="inlineStr">
+      <c r="E5" s="6" t="inlineStr">
         <is>
           <t>Kalenji noir</t>
         </is>
       </c>
-      <c r="F5" s="6" t="inlineStr">
-        <is>
-          <t>Inventé : exter</t>
-        </is>
-      </c>
     </row>
     <row r="6">
-      <c r="A6" s="8" t="n">
+      <c r="A6" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="9" t="inlineStr">
+      <c r="B6" s="8" t="inlineStr">
         <is>
           <t>CARON</t>
         </is>
       </c>
-      <c r="C6" s="10" t="inlineStr">
+      <c r="C6" s="9" t="inlineStr">
         <is>
           <t>Alvin</t>
         </is>
       </c>
-      <c r="D6" s="10" t="inlineStr">
+      <c r="D6" s="9" t="inlineStr">
         <is>
           <t>TDDT noir</t>
         </is>
       </c>
-      <c r="E6" s="10" t="inlineStr">
+      <c r="E6" s="9" t="inlineStr">
         <is>
           <t>Kalenji noir</t>
         </is>
       </c>
-      <c r="F6" s="10" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
@@ -665,39 +640,29 @@
           <t>Adidas violet</t>
         </is>
       </c>
-      <c r="F7" s="6" t="inlineStr">
-        <is>
-          <t>Adidas violet : inter/exter non précisé</t>
-        </is>
-      </c>
     </row>
     <row r="8">
-      <c r="A8" s="8" t="n">
+      <c r="A8" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="9" t="inlineStr">
+      <c r="B8" s="8" t="inlineStr">
         <is>
           <t>DELATTRE</t>
         </is>
       </c>
-      <c r="C8" s="10" t="inlineStr">
+      <c r="C8" s="9" t="inlineStr">
         <is>
           <t>Lucenzo</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="D8" s="9" t="inlineStr">
         <is>
           <t>Adidas violet</t>
         </is>
       </c>
-      <c r="E8" s="10" t="inlineStr">
+      <c r="E8" s="9" t="inlineStr">
         <is>
           <t>Nike TN noir</t>
-        </is>
-      </c>
-      <c r="F8" s="10" t="inlineStr">
-        <is>
-          <t>Inventé : inter</t>
         </is>
       </c>
     </row>
@@ -725,35 +690,29 @@
           <t>Puma noir</t>
         </is>
       </c>
-      <c r="F9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="8" t="n">
+      <c r="A10" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="9" t="inlineStr">
+      <c r="B10" s="8" t="inlineStr">
         <is>
           <t>DEROEUX</t>
         </is>
       </c>
-      <c r="C10" s="10" t="inlineStr">
+      <c r="C10" s="9" t="inlineStr">
         <is>
           <t>Aaron</t>
         </is>
       </c>
-      <c r="D10" s="10" t="inlineStr">
+      <c r="D10" s="9" t="inlineStr">
         <is>
           <t>Kamma bleu</t>
         </is>
       </c>
-      <c r="E10" s="10" t="inlineStr">
+      <c r="E10" s="9" t="inlineStr">
         <is>
           <t>Kalenji gris/vert</t>
-        </is>
-      </c>
-      <c r="F10" s="10" t="inlineStr">
-        <is>
-          <t>Kalenji : inter/exter non précisé</t>
         </is>
       </c>
     </row>
@@ -781,33 +740,31 @@
           <t>Lacoste noir</t>
         </is>
       </c>
-      <c r="F11" s="6" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="8" t="n">
+      <c r="A12" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="B12" s="9" t="inlineStr">
+      <c r="B12" s="8" t="inlineStr">
         <is>
           <t>DEVAUCHELLE</t>
         </is>
       </c>
-      <c r="C12" s="10" t="inlineStr">
+      <c r="C12" s="9" t="inlineStr">
         <is>
           <t>Tyméo</t>
         </is>
       </c>
-      <c r="D12" s="10" t="inlineStr">
+      <c r="D12" s="9" t="inlineStr">
         <is>
           <t>Asics blanche</t>
         </is>
       </c>
-      <c r="E12" s="10" t="inlineStr">
+      <c r="E12" s="9" t="inlineStr">
         <is>
           <t>Adidas noir</t>
         </is>
       </c>
-      <c r="F12" s="10" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
@@ -833,33 +790,31 @@
           <t>Nike bleu/vert</t>
         </is>
       </c>
-      <c r="F13" s="6" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="8" t="n">
+      <c r="A14" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="B14" s="9" t="inlineStr">
+      <c r="B14" s="8" t="inlineStr">
         <is>
           <t>DUFOUR</t>
         </is>
       </c>
-      <c r="C14" s="10" t="inlineStr">
+      <c r="C14" s="9" t="inlineStr">
         <is>
           <t>Marie</t>
         </is>
       </c>
-      <c r="D14" s="10" t="inlineStr">
+      <c r="D14" s="9" t="inlineStr">
         <is>
           <t>Nike violet clair</t>
         </is>
       </c>
-      <c r="E14" s="10" t="inlineStr">
+      <c r="E14" s="9" t="inlineStr">
         <is>
           <t>Puma noir/rose</t>
         </is>
       </c>
-      <c r="F14" s="10" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
@@ -885,35 +840,29 @@
           <t>5 Miles noir</t>
         </is>
       </c>
-      <c r="F15" s="6" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="8" t="n">
+      <c r="A16" s="7" t="n">
         <v>12</v>
       </c>
-      <c r="B16" s="9" t="inlineStr">
+      <c r="B16" s="8" t="inlineStr">
         <is>
           <t>DUPONT</t>
         </is>
       </c>
-      <c r="C16" s="10" t="inlineStr">
+      <c r="C16" s="9" t="inlineStr">
         <is>
           <t>Alban</t>
         </is>
       </c>
-      <c r="D16" s="10" t="inlineStr">
+      <c r="D16" s="9" t="inlineStr">
         <is>
           <t>Asics bleu</t>
         </is>
       </c>
-      <c r="E16" s="10" t="inlineStr">
+      <c r="E16" s="9" t="inlineStr">
         <is>
           <t>NB noir</t>
-        </is>
-      </c>
-      <c r="F16" s="10" t="inlineStr">
-        <is>
-          <t>NB : inter/exter non précisé</t>
         </is>
       </c>
     </row>
@@ -941,35 +890,29 @@
           <t>Asics noir</t>
         </is>
       </c>
-      <c r="F17" s="6" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="8" t="n">
+      <c r="A18" s="7" t="n">
         <v>14</v>
       </c>
-      <c r="B18" s="9" t="inlineStr">
+      <c r="B18" s="8" t="inlineStr">
         <is>
           <t>GELE</t>
         </is>
       </c>
-      <c r="C18" s="10" t="inlineStr">
+      <c r="C18" s="9" t="inlineStr">
         <is>
           <t>Yanis</t>
         </is>
       </c>
-      <c r="D18" s="10" t="inlineStr">
+      <c r="D18" s="9" t="inlineStr">
         <is>
           <t>F50 blanche</t>
         </is>
       </c>
-      <c r="E18" s="7" t="inlineStr">
+      <c r="E18" s="9" t="inlineStr">
         <is>
           <t>NB noir/orange</t>
-        </is>
-      </c>
-      <c r="F18" s="10" t="inlineStr">
-        <is>
-          <t>Inventé : exter</t>
         </is>
       </c>
     </row>
@@ -997,33 +940,31 @@
           <t>Asics gris/vert</t>
         </is>
       </c>
-      <c r="F19" s="6" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="8" t="n">
+      <c r="A20" s="7" t="n">
         <v>16</v>
       </c>
-      <c r="B20" s="9" t="inlineStr">
+      <c r="B20" s="8" t="inlineStr">
         <is>
           <t>HENRY</t>
         </is>
       </c>
-      <c r="C20" s="10" t="inlineStr">
+      <c r="C20" s="9" t="inlineStr">
         <is>
           <t>Nathanaël</t>
         </is>
       </c>
-      <c r="D20" s="10" t="inlineStr">
+      <c r="D20" s="9" t="inlineStr">
         <is>
           <t>Décathlon bleu</t>
         </is>
       </c>
-      <c r="E20" s="10" t="inlineStr">
+      <c r="E20" s="9" t="inlineStr">
         <is>
           <t>Asics bleu</t>
         </is>
       </c>
-      <c r="F20" s="10" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="4" t="n">
@@ -1049,33 +990,31 @@
           <t>Nike noir/doré</t>
         </is>
       </c>
-      <c r="F21" s="6" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="8" t="n">
+      <c r="A22" s="7" t="n">
         <v>18</v>
       </c>
-      <c r="B22" s="9" t="inlineStr">
+      <c r="B22" s="8" t="inlineStr">
         <is>
           <t>LASSALLE</t>
         </is>
       </c>
-      <c r="C22" s="10" t="inlineStr">
+      <c r="C22" s="9" t="inlineStr">
         <is>
           <t>Mathys</t>
         </is>
       </c>
-      <c r="D22" s="10" t="inlineStr">
+      <c r="D22" s="9" t="inlineStr">
         <is>
           <t>Adidas noir/blanc</t>
         </is>
       </c>
-      <c r="E22" s="10" t="inlineStr">
+      <c r="E22" s="9" t="inlineStr">
         <is>
           <t>Adidas noir</t>
         </is>
       </c>
-      <c r="F22" s="10" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="4" t="n">
@@ -1101,37 +1040,31 @@
           <t>Kalenji gris</t>
         </is>
       </c>
-      <c r="F23" s="6" t="inlineStr">
-        <is>
-          <t>Kalenji gris : inter/exter non précisé</t>
-        </is>
-      </c>
     </row>
     <row r="24">
-      <c r="A24" s="8" t="n">
+      <c r="A24" s="7" t="n">
         <v>20</v>
       </c>
-      <c r="B24" s="9" t="inlineStr">
+      <c r="B24" s="8" t="inlineStr">
         <is>
           <t>MEILLIEZ</t>
         </is>
       </c>
-      <c r="C24" s="10" t="inlineStr">
+      <c r="C24" s="9" t="inlineStr">
         <is>
           <t>Antoine</t>
         </is>
       </c>
-      <c r="D24" s="10" t="inlineStr">
+      <c r="D24" s="9" t="inlineStr">
         <is>
           <t>Adidas blanc/bleu</t>
         </is>
       </c>
-      <c r="E24" s="10" t="inlineStr">
+      <c r="E24" s="9" t="inlineStr">
         <is>
           <t>Energetics noir</t>
         </is>
       </c>
-      <c r="F24" s="10" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="4" t="n">
@@ -1157,35 +1090,29 @@
           <t>Camps U blanche</t>
         </is>
       </c>
-      <c r="F25" s="6" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="8" t="n">
+      <c r="A26" s="7" t="n">
         <v>22</v>
       </c>
-      <c r="B26" s="9" t="inlineStr">
+      <c r="B26" s="8" t="inlineStr">
         <is>
           <t>RICQUE</t>
         </is>
       </c>
-      <c r="C26" s="10" t="inlineStr">
+      <c r="C26" s="9" t="inlineStr">
         <is>
           <t>Ethan</t>
         </is>
       </c>
-      <c r="D26" s="10" t="inlineStr">
+      <c r="D26" s="9" t="inlineStr">
         <is>
           <t>Adidas noir</t>
         </is>
       </c>
-      <c r="E26" s="7" t="inlineStr">
+      <c r="E26" s="9" t="inlineStr">
         <is>
           <t>Kalenji gris</t>
-        </is>
-      </c>
-      <c r="F26" s="10" t="inlineStr">
-        <is>
-          <t>Inventé : exter</t>
         </is>
       </c>
     </row>
@@ -1213,33 +1140,31 @@
           <t>Nike bleu</t>
         </is>
       </c>
-      <c r="F27" s="6" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="8" t="n">
+      <c r="A28" s="7" t="n">
         <v>24</v>
       </c>
-      <c r="B28" s="9" t="inlineStr">
+      <c r="B28" s="8" t="inlineStr">
         <is>
           <t>ROUGEGREZ</t>
         </is>
       </c>
-      <c r="C28" s="10" t="inlineStr">
+      <c r="C28" s="9" t="inlineStr">
         <is>
           <t>Maël</t>
         </is>
       </c>
-      <c r="D28" s="10" t="inlineStr">
+      <c r="D28" s="9" t="inlineStr">
         <is>
           <t>Unyk noir/bleu</t>
         </is>
       </c>
-      <c r="E28" s="10" t="inlineStr">
+      <c r="E28" s="9" t="inlineStr">
         <is>
           <t>Décathlon noir</t>
         </is>
       </c>
-      <c r="F28" s="10" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="4" t="n">
@@ -1265,33 +1190,31 @@
           <t>5 Miles bleu</t>
         </is>
       </c>
-      <c r="F29" s="6" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="8" t="n">
+      <c r="A30" s="7" t="n">
         <v>26</v>
       </c>
-      <c r="B30" s="9" t="inlineStr">
+      <c r="B30" s="8" t="inlineStr">
         <is>
           <t>WYCKAERT</t>
         </is>
       </c>
-      <c r="C30" s="10" t="inlineStr">
+      <c r="C30" s="9" t="inlineStr">
         <is>
           <t>Lucas</t>
         </is>
       </c>
-      <c r="D30" s="10" t="inlineStr">
+      <c r="D30" s="9" t="inlineStr">
         <is>
           <t>NB orange</t>
         </is>
       </c>
-      <c r="E30" s="10" t="inlineStr">
+      <c r="E30" s="9" t="inlineStr">
         <is>
           <t>Nike vert/gris</t>
         </is>
       </c>
-      <c r="F30" s="10" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="4" t="n">
@@ -1315,11 +1238,6 @@
       <c r="E31" s="6" t="inlineStr">
         <is>
           <t>Nike gris</t>
-        </is>
-      </c>
-      <c r="F31" s="6" t="inlineStr">
-        <is>
-          <t>Prénom dans ta liste mais absent de la classe Ecole Directe</t>
         </is>
       </c>
     </row>
@@ -1334,7 +1252,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F36"/>
+  <dimension ref="A1:E36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1342,7 +1260,6 @@
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="26" customWidth="1" min="4" max="4"/>
     <col width="26" customWidth="1" min="5" max="5"/>
-    <col width="48" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1355,7 +1272,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Case orange = paire inventée (reprise d'une autre paire de la liste)  ·  Case grise = dispensé</t>
+          <t>Case grise = dispensé</t>
         </is>
       </c>
     </row>
@@ -1383,11 +1300,6 @@
       <c r="E4" s="3" t="inlineStr">
         <is>
           <t>Baskets extérieur</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>Remarque</t>
         </is>
       </c>
     </row>
@@ -1415,33 +1327,31 @@
           <t>Crane gris</t>
         </is>
       </c>
-      <c r="F5" s="6" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="8" t="n">
+      <c r="A6" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="9" t="inlineStr">
+      <c r="B6" s="8" t="inlineStr">
         <is>
           <t>BOUCHERAT</t>
         </is>
       </c>
-      <c r="C6" s="10" t="inlineStr">
+      <c r="C6" s="9" t="inlineStr">
         <is>
           <t>Bastien</t>
         </is>
       </c>
-      <c r="D6" s="10" t="inlineStr">
+      <c r="D6" s="9" t="inlineStr">
         <is>
           <t>Décathlon blanche</t>
         </is>
       </c>
-      <c r="E6" s="10" t="inlineStr">
+      <c r="E6" s="9" t="inlineStr">
         <is>
           <t>Puma gris</t>
         </is>
       </c>
-      <c r="F6" s="10" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
@@ -1467,33 +1377,31 @@
           <t>Nike jaune</t>
         </is>
       </c>
-      <c r="F7" s="6" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="8" t="n">
+      <c r="A8" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="9" t="inlineStr">
+      <c r="B8" s="8" t="inlineStr">
         <is>
           <t>CORRE</t>
         </is>
       </c>
-      <c r="C8" s="10" t="inlineStr">
+      <c r="C8" s="9" t="inlineStr">
         <is>
           <t>Maël</t>
         </is>
       </c>
-      <c r="D8" s="10" t="inlineStr">
+      <c r="D8" s="9" t="inlineStr">
         <is>
           <t>Nike beige</t>
         </is>
       </c>
-      <c r="E8" s="10" t="inlineStr">
+      <c r="E8" s="9" t="inlineStr">
         <is>
           <t>Adidas noir</t>
         </is>
       </c>
-      <c r="F8" s="10" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
@@ -1519,33 +1427,31 @@
           <t>Adidas noir</t>
         </is>
       </c>
-      <c r="F9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="8" t="n">
+      <c r="A10" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="9" t="inlineStr">
+      <c r="B10" s="8" t="inlineStr">
         <is>
           <t>DE VULDER</t>
         </is>
       </c>
-      <c r="C10" s="10" t="inlineStr">
+      <c r="C10" s="9" t="inlineStr">
         <is>
           <t>Amaury</t>
         </is>
       </c>
-      <c r="D10" s="10" t="inlineStr">
+      <c r="D10" s="9" t="inlineStr">
         <is>
           <t>Asics noir</t>
         </is>
       </c>
-      <c r="E10" s="10" t="inlineStr">
+      <c r="E10" s="9" t="inlineStr">
         <is>
           <t>Energetics</t>
         </is>
       </c>
-      <c r="F10" s="10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
@@ -1571,35 +1477,29 @@
           <t>Adidas bleu</t>
         </is>
       </c>
-      <c r="F11" s="6" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="8" t="n">
+      <c r="A12" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="B12" s="9" t="inlineStr">
+      <c r="B12" s="8" t="inlineStr">
         <is>
           <t>DELEPIERRE</t>
         </is>
       </c>
-      <c r="C12" s="10" t="inlineStr">
+      <c r="C12" s="9" t="inlineStr">
         <is>
           <t>Cézanne</t>
         </is>
       </c>
-      <c r="D12" s="10" t="inlineStr">
+      <c r="D12" s="9" t="inlineStr">
         <is>
           <t>Nike noir</t>
         </is>
       </c>
-      <c r="E12" s="7" t="inlineStr">
+      <c r="E12" s="9" t="inlineStr">
         <is>
           <t>Asics rose</t>
-        </is>
-      </c>
-      <c r="F12" s="10" t="inlineStr">
-        <is>
-          <t>Inventé : exter</t>
         </is>
       </c>
     </row>
@@ -1622,42 +1522,36 @@
           <t>Nike noir/orange</t>
         </is>
       </c>
-      <c r="E13" s="7" t="inlineStr">
+      <c r="E13" s="6" t="inlineStr">
         <is>
           <t>Adidas gris/rose</t>
         </is>
       </c>
-      <c r="F13" s="6" t="inlineStr">
-        <is>
-          <t>Inventé : exter</t>
-        </is>
-      </c>
     </row>
     <row r="14">
-      <c r="A14" s="8" t="n">
+      <c r="A14" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="B14" s="9" t="inlineStr">
+      <c r="B14" s="8" t="inlineStr">
         <is>
           <t>DERHILLE</t>
         </is>
       </c>
-      <c r="C14" s="10" t="inlineStr">
+      <c r="C14" s="9" t="inlineStr">
         <is>
           <t>Thibaud</t>
         </is>
       </c>
-      <c r="D14" s="10" t="inlineStr">
+      <c r="D14" s="9" t="inlineStr">
         <is>
           <t>Asics bleu/noir</t>
         </is>
       </c>
-      <c r="E14" s="10" t="inlineStr">
+      <c r="E14" s="9" t="inlineStr">
         <is>
           <t>Asics blanche</t>
         </is>
       </c>
-      <c r="F14" s="10" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
@@ -1678,42 +1572,36 @@
           <t>Kalenji bleu</t>
         </is>
       </c>
-      <c r="E15" s="7" t="inlineStr">
+      <c r="E15" s="6" t="inlineStr">
         <is>
           <t>Kalenji bleu</t>
         </is>
       </c>
-      <c r="F15" s="6" t="inlineStr">
-        <is>
-          <t>Inventé : exter</t>
-        </is>
-      </c>
     </row>
     <row r="16">
-      <c r="A16" s="8" t="n">
+      <c r="A16" s="7" t="n">
         <v>12</v>
       </c>
-      <c r="B16" s="9" t="inlineStr">
+      <c r="B16" s="8" t="inlineStr">
         <is>
           <t>DUHAMEL</t>
         </is>
       </c>
-      <c r="C16" s="10" t="inlineStr">
+      <c r="C16" s="9" t="inlineStr">
         <is>
           <t>Rémi</t>
         </is>
       </c>
-      <c r="D16" s="10" t="inlineStr">
+      <c r="D16" s="9" t="inlineStr">
         <is>
           <t>Puma blanche</t>
         </is>
       </c>
-      <c r="E16" s="10" t="inlineStr">
+      <c r="E16" s="9" t="inlineStr">
         <is>
           <t>Adidas noir</t>
         </is>
       </c>
-      <c r="F16" s="10" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="4" t="n">
@@ -1739,33 +1627,31 @@
           <t>Kalenji gris/orange</t>
         </is>
       </c>
-      <c r="F17" s="6" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="8" t="n">
+      <c r="A18" s="7" t="n">
         <v>14</v>
       </c>
-      <c r="B18" s="9" t="inlineStr">
+      <c r="B18" s="8" t="inlineStr">
         <is>
           <t>ELIE</t>
         </is>
       </c>
-      <c r="C18" s="10" t="inlineStr">
+      <c r="C18" s="9" t="inlineStr">
         <is>
           <t>Quantin</t>
         </is>
       </c>
-      <c r="D18" s="10" t="inlineStr">
+      <c r="D18" s="9" t="inlineStr">
         <is>
           <t>Nike noir</t>
         </is>
       </c>
-      <c r="E18" s="10" t="inlineStr">
+      <c r="E18" s="9" t="inlineStr">
         <is>
           <t>Nike beige/blanc</t>
         </is>
       </c>
-      <c r="F18" s="10" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="4" t="n">
@@ -1791,33 +1677,31 @@
           <t>Crampons</t>
         </is>
       </c>
-      <c r="F19" s="6" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="8" t="n">
+      <c r="A20" s="7" t="n">
         <v>16</v>
       </c>
-      <c r="B20" s="9" t="inlineStr">
+      <c r="B20" s="8" t="inlineStr">
         <is>
           <t>HENNIAUX</t>
         </is>
       </c>
-      <c r="C20" s="10" t="inlineStr">
+      <c r="C20" s="9" t="inlineStr">
         <is>
           <t>Maxime</t>
         </is>
       </c>
-      <c r="D20" s="10" t="inlineStr">
+      <c r="D20" s="9" t="inlineStr">
         <is>
           <t>Adidas vert pomme</t>
         </is>
       </c>
-      <c r="E20" s="10" t="inlineStr">
+      <c r="E20" s="9" t="inlineStr">
         <is>
           <t>Adidas noir/bleu</t>
         </is>
       </c>
-      <c r="F20" s="10" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="4" t="n">
@@ -1838,42 +1722,36 @@
           <t>Adidas beige</t>
         </is>
       </c>
-      <c r="E21" s="7" t="inlineStr">
+      <c r="E21" s="6" t="inlineStr">
         <is>
           <t>Asics noir</t>
         </is>
       </c>
-      <c r="F21" s="6" t="inlineStr">
-        <is>
-          <t>Inventé : exter</t>
-        </is>
-      </c>
     </row>
     <row r="22">
-      <c r="A22" s="8" t="n">
+      <c r="A22" s="7" t="n">
         <v>18</v>
       </c>
-      <c r="B22" s="9" t="inlineStr">
+      <c r="B22" s="8" t="inlineStr">
         <is>
           <t>JONARD</t>
         </is>
       </c>
-      <c r="C22" s="10" t="inlineStr">
+      <c r="C22" s="9" t="inlineStr">
         <is>
           <t>Théo</t>
         </is>
       </c>
-      <c r="D22" s="10" t="inlineStr">
+      <c r="D22" s="9" t="inlineStr">
         <is>
           <t>Kalenji blanche</t>
         </is>
       </c>
-      <c r="E22" s="10" t="inlineStr">
+      <c r="E22" s="9" t="inlineStr">
         <is>
           <t>Kalenji gris</t>
         </is>
       </c>
-      <c r="F22" s="10" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="4" t="n">
@@ -1899,33 +1777,31 @@
           <t>Kalenji noir/vert</t>
         </is>
       </c>
-      <c r="F23" s="6" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="8" t="n">
+      <c r="A24" s="7" t="n">
         <v>20</v>
       </c>
-      <c r="B24" s="9" t="inlineStr">
+      <c r="B24" s="8" t="inlineStr">
         <is>
           <t>LEMONNIER</t>
         </is>
       </c>
-      <c r="C24" s="10" t="inlineStr">
+      <c r="C24" s="9" t="inlineStr">
         <is>
           <t>Valentin</t>
         </is>
       </c>
-      <c r="D24" s="10" t="inlineStr">
+      <c r="D24" s="9" t="inlineStr">
         <is>
           <t>Adidas bleu</t>
         </is>
       </c>
-      <c r="E24" s="10" t="inlineStr">
+      <c r="E24" s="9" t="inlineStr">
         <is>
           <t>Nike noir</t>
         </is>
       </c>
-      <c r="F24" s="10" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="4" t="n">
@@ -1951,33 +1827,31 @@
           <t>NB noir/orange</t>
         </is>
       </c>
-      <c r="F25" s="6" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="8" t="n">
+      <c r="A26" s="7" t="n">
         <v>22</v>
       </c>
-      <c r="B26" s="9" t="inlineStr">
+      <c r="B26" s="8" t="inlineStr">
         <is>
           <t>LEROY-BAUDRILLARD</t>
         </is>
       </c>
-      <c r="C26" s="10" t="inlineStr">
+      <c r="C26" s="9" t="inlineStr">
         <is>
           <t>Noah</t>
         </is>
       </c>
-      <c r="D26" s="10" t="inlineStr">
+      <c r="D26" s="9" t="inlineStr">
         <is>
           <t>Adidas blanc/gris</t>
         </is>
       </c>
-      <c r="E26" s="10" t="inlineStr">
+      <c r="E26" s="9" t="inlineStr">
         <is>
           <t>Adidas noir</t>
         </is>
       </c>
-      <c r="F26" s="10" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="4" t="n">
@@ -2003,35 +1877,29 @@
           <t>Puma blanche</t>
         </is>
       </c>
-      <c r="F27" s="6" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="8" t="n">
+      <c r="A28" s="7" t="n">
         <v>24</v>
       </c>
-      <c r="B28" s="9" t="inlineStr">
+      <c r="B28" s="8" t="inlineStr">
         <is>
           <t>LUCIDARME</t>
         </is>
       </c>
-      <c r="C28" s="10" t="inlineStr">
+      <c r="C28" s="9" t="inlineStr">
         <is>
           <t>Louise</t>
         </is>
       </c>
-      <c r="D28" s="10" t="inlineStr">
+      <c r="D28" s="9" t="inlineStr">
         <is>
           <t>Nike blanche</t>
         </is>
       </c>
-      <c r="E28" s="10" t="inlineStr">
+      <c r="E28" s="9" t="inlineStr">
         <is>
           <t>Salomon</t>
-        </is>
-      </c>
-      <c r="F28" s="10" t="inlineStr">
-        <is>
-          <t>Notée « Louis » dans ta liste</t>
         </is>
       </c>
     </row>
@@ -2059,33 +1927,31 @@
           <t>Kalenji noir</t>
         </is>
       </c>
-      <c r="F29" s="6" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="8" t="n">
+      <c r="A30" s="7" t="n">
         <v>26</v>
       </c>
-      <c r="B30" s="9" t="inlineStr">
+      <c r="B30" s="8" t="inlineStr">
         <is>
           <t>MIGOTTO</t>
         </is>
       </c>
-      <c r="C30" s="10" t="inlineStr">
+      <c r="C30" s="9" t="inlineStr">
         <is>
           <t>Nathan</t>
         </is>
       </c>
-      <c r="D30" s="10" t="inlineStr">
+      <c r="D30" s="9" t="inlineStr">
         <is>
           <t>Asics vert/bleu</t>
         </is>
       </c>
-      <c r="E30" s="10" t="inlineStr">
+      <c r="E30" s="9" t="inlineStr">
         <is>
           <t>Nike noir</t>
         </is>
       </c>
-      <c r="F30" s="10" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="4" t="n">
@@ -2111,35 +1977,29 @@
           <t>Unyk noir</t>
         </is>
       </c>
-      <c r="F31" s="6" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="8" t="n">
+      <c r="A32" s="7" t="n">
         <v>28</v>
       </c>
-      <c r="B32" s="9" t="inlineStr">
+      <c r="B32" s="8" t="inlineStr">
         <is>
           <t>SCAILLIERE</t>
         </is>
       </c>
-      <c r="C32" s="10" t="inlineStr">
+      <c r="C32" s="9" t="inlineStr">
         <is>
           <t>Anaïs</t>
         </is>
       </c>
-      <c r="D32" s="12" t="inlineStr">
+      <c r="D32" s="11" t="inlineStr">
         <is>
           <t>Dispensé</t>
         </is>
       </c>
-      <c r="E32" s="12" t="inlineStr">
+      <c r="E32" s="11" t="inlineStr">
         <is>
           <t>Dispensé</t>
-        </is>
-      </c>
-      <c r="F32" s="10" t="inlineStr">
-        <is>
-          <t>Dispensée</t>
         </is>
       </c>
     </row>
@@ -2167,33 +2027,31 @@
           <t>NB gris/orange</t>
         </is>
       </c>
-      <c r="F33" s="6" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="8" t="n">
+      <c r="A34" s="7" t="n">
         <v>30</v>
       </c>
-      <c r="B34" s="9" t="inlineStr">
+      <c r="B34" s="8" t="inlineStr">
         <is>
           <t>TOP</t>
         </is>
       </c>
-      <c r="C34" s="10" t="inlineStr">
+      <c r="C34" s="9" t="inlineStr">
         <is>
           <t>Tédy</t>
         </is>
       </c>
-      <c r="D34" s="10" t="inlineStr">
+      <c r="D34" s="9" t="inlineStr">
         <is>
           <t>Décathlon bleu</t>
         </is>
       </c>
-      <c r="E34" s="10" t="inlineStr">
+      <c r="E34" s="9" t="inlineStr">
         <is>
           <t>Energetics noir/rouge</t>
         </is>
       </c>
-      <c r="F34" s="10" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="4" t="n">
@@ -2209,7 +2067,7 @@
           <t>Baptiste</t>
         </is>
       </c>
-      <c r="D35" s="7" t="inlineStr">
+      <c r="D35" s="6" t="inlineStr">
         <is>
           <t>Artengo blanche</t>
         </is>
@@ -2219,37 +2077,31 @@
           <t>Asics gris/jaune</t>
         </is>
       </c>
-      <c r="F35" s="6" t="inlineStr">
-        <is>
-          <t>Inventé : inter</t>
-        </is>
-      </c>
     </row>
     <row r="36">
-      <c r="A36" s="8" t="n">
+      <c r="A36" s="7" t="n">
         <v>32</v>
       </c>
-      <c r="B36" s="9" t="inlineStr">
+      <c r="B36" s="8" t="inlineStr">
         <is>
           <t>VANDOIS</t>
         </is>
       </c>
-      <c r="C36" s="10" t="inlineStr">
+      <c r="C36" s="9" t="inlineStr">
         <is>
           <t>Théo</t>
         </is>
       </c>
-      <c r="D36" s="10" t="inlineStr">
+      <c r="D36" s="9" t="inlineStr">
         <is>
           <t>Asics noir</t>
         </is>
       </c>
-      <c r="E36" s="10" t="inlineStr">
+      <c r="E36" s="9" t="inlineStr">
         <is>
           <t>Asics noir</t>
         </is>
       </c>
-      <c r="F36" s="10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2262,7 +2114,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2271,7 +2123,6 @@
     <col width="26" customWidth="1" min="4" max="4"/>
     <col width="26" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="48" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2284,7 +2135,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Case orange = paire inventée (reprise d'une autre paire de la liste)  ·  Case grise = dispensé</t>
+          <t>Case grise = dispensé</t>
         </is>
       </c>
     </row>
@@ -2317,11 +2168,6 @@
       <c r="F4" s="3" t="inlineStr">
         <is>
           <t>Activité</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>Remarque</t>
         </is>
       </c>
     </row>
@@ -2354,38 +2200,36 @@
           <t>NON</t>
         </is>
       </c>
-      <c r="G5" s="6" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="8" t="n">
+      <c r="A6" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="9" t="inlineStr">
+      <c r="B6" s="8" t="inlineStr">
         <is>
           <t>BRODA</t>
         </is>
       </c>
-      <c r="C6" s="10" t="inlineStr">
+      <c r="C6" s="9" t="inlineStr">
         <is>
           <t>Mélys</t>
         </is>
       </c>
-      <c r="D6" s="10" t="inlineStr">
+      <c r="D6" s="9" t="inlineStr">
         <is>
           <t>Kalenji rose</t>
         </is>
       </c>
-      <c r="E6" s="10" t="inlineStr">
+      <c r="E6" s="9" t="inlineStr">
         <is>
           <t>Kalenji noir</t>
         </is>
       </c>
-      <c r="F6" s="10" t="inlineStr">
+      <c r="F6" s="9" t="inlineStr">
         <is>
           <t>Athlétisme</t>
         </is>
       </c>
-      <c r="G6" s="10" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
@@ -2416,40 +2260,34 @@
           <t>NON</t>
         </is>
       </c>
-      <c r="G7" s="6" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="8" t="n">
+      <c r="A8" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="9" t="inlineStr">
+      <c r="B8" s="8" t="inlineStr">
         <is>
           <t>DEBUIRE</t>
         </is>
       </c>
-      <c r="C8" s="10" t="inlineStr">
+      <c r="C8" s="9" t="inlineStr">
         <is>
           <t>Victor</t>
         </is>
       </c>
-      <c r="D8" s="10" t="inlineStr">
+      <c r="D8" s="9" t="inlineStr">
         <is>
           <t>Adidas blanche</t>
         </is>
       </c>
-      <c r="E8" s="10" t="inlineStr">
+      <c r="E8" s="9" t="inlineStr">
         <is>
           <t>Asics noir</t>
         </is>
       </c>
-      <c r="F8" s="10" t="inlineStr">
+      <c r="F8" s="9" t="inlineStr">
         <is>
           <t>NON</t>
-        </is>
-      </c>
-      <c r="G8" s="10" t="inlineStr">
-        <is>
-          <t>Asics : inter/exter non précisé</t>
         </is>
       </c>
     </row>
@@ -2482,38 +2320,36 @@
           <t>Natation</t>
         </is>
       </c>
-      <c r="G9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="8" t="n">
+      <c r="A10" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="9" t="inlineStr">
+      <c r="B10" s="8" t="inlineStr">
         <is>
           <t>DESPICHT</t>
         </is>
       </c>
-      <c r="C10" s="10" t="inlineStr">
+      <c r="C10" s="9" t="inlineStr">
         <is>
           <t>Pauline</t>
         </is>
       </c>
-      <c r="D10" s="10" t="inlineStr">
+      <c r="D10" s="9" t="inlineStr">
         <is>
           <t>NB blanche</t>
         </is>
       </c>
-      <c r="E10" s="10" t="inlineStr">
+      <c r="E10" s="9" t="inlineStr">
         <is>
           <t>Asics rose</t>
         </is>
       </c>
-      <c r="F10" s="10" t="inlineStr">
+      <c r="F10" s="9" t="inlineStr">
         <is>
           <t>Badminton</t>
         </is>
       </c>
-      <c r="G10" s="10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
@@ -2544,42 +2380,36 @@
           <t>Tennis de table</t>
         </is>
       </c>
-      <c r="G11" s="6" t="inlineStr">
-        <is>
-          <t>Unyk : inter/exter non précisé</t>
-        </is>
-      </c>
     </row>
     <row r="12">
-      <c r="A12" s="8" t="n">
+      <c r="A12" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="B12" s="9" t="inlineStr">
+      <c r="B12" s="8" t="inlineStr">
         <is>
           <t>DEWYNTER-BEAUVAIS</t>
         </is>
       </c>
-      <c r="C12" s="10" t="inlineStr">
+      <c r="C12" s="9" t="inlineStr">
         <is>
           <t>Léo</t>
         </is>
       </c>
-      <c r="D12" s="10" t="inlineStr">
+      <c r="D12" s="9" t="inlineStr">
         <is>
           <t>Blanche (marque ?)</t>
         </is>
       </c>
-      <c r="E12" s="10" t="inlineStr">
+      <c r="E12" s="9" t="inlineStr">
         <is>
           <t>Féethir noir</t>
         </is>
       </c>
-      <c r="F12" s="10" t="inlineStr">
+      <c r="F12" s="9" t="inlineStr">
         <is>
           <t>NON</t>
         </is>
       </c>
-      <c r="G12" s="10" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
@@ -2610,38 +2440,36 @@
           <t>NON</t>
         </is>
       </c>
-      <c r="G13" s="6" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="8" t="n">
+      <c r="A14" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="B14" s="9" t="inlineStr">
+      <c r="B14" s="8" t="inlineStr">
         <is>
           <t>GERASCH</t>
         </is>
       </c>
-      <c r="C14" s="10" t="inlineStr">
+      <c r="C14" s="9" t="inlineStr">
         <is>
           <t>Evan</t>
         </is>
       </c>
-      <c r="D14" s="10" t="inlineStr">
+      <c r="D14" s="9" t="inlineStr">
         <is>
           <t>Adidas gris &amp; blanc</t>
         </is>
       </c>
-      <c r="E14" s="10" t="inlineStr">
+      <c r="E14" s="9" t="inlineStr">
         <is>
           <t>Asics blanche</t>
         </is>
       </c>
-      <c r="F14" s="10" t="inlineStr">
+      <c r="F14" s="9" t="inlineStr">
         <is>
           <t>NON</t>
         </is>
       </c>
-      <c r="G14" s="10" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
@@ -2672,38 +2500,36 @@
           <t>Combat</t>
         </is>
       </c>
-      <c r="G15" s="6" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="8" t="n">
+      <c r="A16" s="7" t="n">
         <v>12</v>
       </c>
-      <c r="B16" s="9" t="inlineStr">
+      <c r="B16" s="8" t="inlineStr">
         <is>
           <t>JOSEFOWICZ</t>
         </is>
       </c>
-      <c r="C16" s="10" t="inlineStr">
+      <c r="C16" s="9" t="inlineStr">
         <is>
           <t>Louis</t>
         </is>
       </c>
-      <c r="D16" s="10" t="inlineStr">
+      <c r="D16" s="9" t="inlineStr">
         <is>
           <t>Adidas bleu</t>
         </is>
       </c>
-      <c r="E16" s="10" t="inlineStr">
+      <c r="E16" s="9" t="inlineStr">
         <is>
           <t>Asics noir</t>
         </is>
       </c>
-      <c r="F16" s="10" t="inlineStr">
+      <c r="F16" s="9" t="inlineStr">
         <is>
           <t>Foot</t>
         </is>
       </c>
-      <c r="G16" s="10" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="4" t="n">
@@ -2734,38 +2560,36 @@
           <t>NON</t>
         </is>
       </c>
-      <c r="G17" s="6" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="8" t="n">
+      <c r="A18" s="7" t="n">
         <v>14</v>
       </c>
-      <c r="B18" s="9" t="inlineStr">
+      <c r="B18" s="8" t="inlineStr">
         <is>
           <t>LEFEVRE COUPE</t>
         </is>
       </c>
-      <c r="C18" s="10" t="inlineStr">
+      <c r="C18" s="9" t="inlineStr">
         <is>
           <t>Elora</t>
         </is>
       </c>
-      <c r="D18" s="10" t="inlineStr">
+      <c r="D18" s="9" t="inlineStr">
         <is>
           <t>Nike rose</t>
         </is>
       </c>
-      <c r="E18" s="10" t="inlineStr">
+      <c r="E18" s="9" t="inlineStr">
         <is>
           <t>Unyk bleu marine</t>
         </is>
       </c>
-      <c r="F18" s="10" t="inlineStr">
+      <c r="F18" s="9" t="inlineStr">
         <is>
           <t>Gym</t>
         </is>
       </c>
-      <c r="G18" s="10" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="4" t="n">
@@ -2796,40 +2620,34 @@
           <t>NON</t>
         </is>
       </c>
-      <c r="G19" s="6" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="8" t="n">
+      <c r="A20" s="7" t="n">
         <v>16</v>
       </c>
-      <c r="B20" s="9" t="inlineStr">
+      <c r="B20" s="8" t="inlineStr">
         <is>
           <t>PLEZ</t>
         </is>
       </c>
-      <c r="C20" s="10" t="inlineStr">
+      <c r="C20" s="9" t="inlineStr">
         <is>
           <t>Gabrielle</t>
         </is>
       </c>
-      <c r="D20" s="7" t="inlineStr">
+      <c r="D20" s="9" t="inlineStr">
         <is>
           <t>Kalenji bleu</t>
         </is>
       </c>
-      <c r="E20" s="7" t="inlineStr">
+      <c r="E20" s="9" t="inlineStr">
         <is>
           <t>Adidas bleu</t>
         </is>
       </c>
-      <c r="F20" s="10" t="inlineStr">
+      <c r="F20" s="9" t="inlineStr">
         <is>
           <t>?</t>
-        </is>
-      </c>
-      <c r="G20" s="10" t="inlineStr">
-        <is>
-          <t>Inventé : inter + exter</t>
         </is>
       </c>
     </row>
@@ -2862,38 +2680,36 @@
           <t>Natation</t>
         </is>
       </c>
-      <c r="G21" s="6" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="8" t="n">
+      <c r="A22" s="7" t="n">
         <v>18</v>
       </c>
-      <c r="B22" s="9" t="inlineStr">
+      <c r="B22" s="8" t="inlineStr">
         <is>
           <t>ROCROY</t>
         </is>
       </c>
-      <c r="C22" s="10" t="inlineStr">
+      <c r="C22" s="9" t="inlineStr">
         <is>
           <t>Ethan</t>
         </is>
       </c>
-      <c r="D22" s="10" t="inlineStr">
+      <c r="D22" s="9" t="inlineStr">
         <is>
           <t>Puma noir</t>
         </is>
       </c>
-      <c r="E22" s="10" t="inlineStr">
+      <c r="E22" s="9" t="inlineStr">
         <is>
           <t>Lotto noir</t>
         </is>
       </c>
-      <c r="F22" s="10" t="inlineStr">
+      <c r="F22" s="9" t="inlineStr">
         <is>
           <t>Foot</t>
         </is>
       </c>
-      <c r="G22" s="10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2906,7 +2722,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:E26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2914,7 +2730,6 @@
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="26" customWidth="1" min="4" max="4"/>
     <col width="26" customWidth="1" min="5" max="5"/>
-    <col width="48" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2927,7 +2742,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Case orange = paire inventée (reprise d'une autre paire de la liste)  ·  Case grise = dispensé</t>
+          <t>Case grise = dispensé</t>
         </is>
       </c>
     </row>
@@ -2955,11 +2770,6 @@
       <c r="E4" s="3" t="inlineStr">
         <is>
           <t>Baskets extérieur</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>Remarque</t>
         </is>
       </c>
     </row>
@@ -2987,33 +2797,31 @@
           <t>Asics violet</t>
         </is>
       </c>
-      <c r="F5" s="6" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="8" t="n">
+      <c r="A6" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="9" t="inlineStr">
+      <c r="B6" s="8" t="inlineStr">
         <is>
           <t>BOUTEILLER</t>
         </is>
       </c>
-      <c r="C6" s="10" t="inlineStr">
+      <c r="C6" s="9" t="inlineStr">
         <is>
           <t>Nathan</t>
         </is>
       </c>
-      <c r="D6" s="10" t="inlineStr">
+      <c r="D6" s="9" t="inlineStr">
         <is>
           <t>Adidas noir</t>
         </is>
       </c>
-      <c r="E6" s="10" t="inlineStr">
+      <c r="E6" s="9" t="inlineStr">
         <is>
           <t>Asics noir</t>
         </is>
       </c>
-      <c r="F6" s="10" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
@@ -3039,33 +2847,31 @@
           <t>Jovas rouge</t>
         </is>
       </c>
-      <c r="F7" s="6" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="8" t="n">
+      <c r="A8" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="9" t="inlineStr">
+      <c r="B8" s="8" t="inlineStr">
         <is>
           <t>CAMUS</t>
         </is>
       </c>
-      <c r="C8" s="10" t="inlineStr">
+      <c r="C8" s="9" t="inlineStr">
         <is>
           <t>Hugo</t>
         </is>
       </c>
-      <c r="D8" s="10" t="inlineStr">
+      <c r="D8" s="9" t="inlineStr">
         <is>
           <t>Adidas orange</t>
         </is>
       </c>
-      <c r="E8" s="10" t="inlineStr">
+      <c r="E8" s="9" t="inlineStr">
         <is>
           <t>Puma noir</t>
         </is>
       </c>
-      <c r="F8" s="10" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
@@ -3091,33 +2897,31 @@
           <t>Criwitz noir</t>
         </is>
       </c>
-      <c r="F9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="8" t="n">
+      <c r="A10" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="9" t="inlineStr">
+      <c r="B10" s="8" t="inlineStr">
         <is>
           <t>DALLERY</t>
         </is>
       </c>
-      <c r="C10" s="10" t="inlineStr">
+      <c r="C10" s="9" t="inlineStr">
         <is>
           <t>Jules</t>
         </is>
       </c>
-      <c r="D10" s="10" t="inlineStr">
+      <c r="D10" s="9" t="inlineStr">
         <is>
           <t>Skechers gris</t>
         </is>
       </c>
-      <c r="E10" s="10" t="inlineStr">
+      <c r="E10" s="9" t="inlineStr">
         <is>
           <t>Skechers bleu</t>
         </is>
       </c>
-      <c r="F10" s="10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
@@ -3143,33 +2947,31 @@
           <t>Asics bleu/vert</t>
         </is>
       </c>
-      <c r="F11" s="6" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="8" t="n">
+      <c r="A12" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="B12" s="9" t="inlineStr">
+      <c r="B12" s="8" t="inlineStr">
         <is>
           <t>DILLY</t>
         </is>
       </c>
-      <c r="C12" s="10" t="inlineStr">
+      <c r="C12" s="9" t="inlineStr">
         <is>
           <t>Louis</t>
         </is>
       </c>
-      <c r="D12" s="10" t="inlineStr">
+      <c r="D12" s="9" t="inlineStr">
         <is>
           <t>Asics noir</t>
         </is>
       </c>
-      <c r="E12" s="10" t="inlineStr">
+      <c r="E12" s="9" t="inlineStr">
         <is>
           <t>Adidas noir</t>
         </is>
       </c>
-      <c r="F12" s="10" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
@@ -3185,47 +2987,41 @@
           <t>Antoine</t>
         </is>
       </c>
-      <c r="D13" s="7" t="inlineStr">
+      <c r="D13" s="6" t="inlineStr">
         <is>
           <t>Adidas bleu</t>
         </is>
       </c>
-      <c r="E13" s="7" t="inlineStr">
+      <c r="E13" s="6" t="inlineStr">
         <is>
           <t>Nike noir</t>
         </is>
       </c>
-      <c r="F13" s="6" t="inlineStr">
-        <is>
-          <t>Inventé : inter + exter</t>
-        </is>
-      </c>
     </row>
     <row r="14">
-      <c r="A14" s="8" t="n">
+      <c r="A14" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="B14" s="9" t="inlineStr">
+      <c r="B14" s="8" t="inlineStr">
         <is>
           <t>FOVEAU</t>
         </is>
       </c>
-      <c r="C14" s="10" t="inlineStr">
+      <c r="C14" s="9" t="inlineStr">
         <is>
           <t>Paul</t>
         </is>
       </c>
-      <c r="D14" s="10" t="inlineStr">
+      <c r="D14" s="9" t="inlineStr">
         <is>
           <t>Nike noir/jaune</t>
         </is>
       </c>
-      <c r="E14" s="10" t="inlineStr">
+      <c r="E14" s="9" t="inlineStr">
         <is>
           <t>Asics noir</t>
         </is>
       </c>
-      <c r="F14" s="10" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
@@ -3251,33 +3047,31 @@
           <t>Puma noir</t>
         </is>
       </c>
-      <c r="F15" s="6" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="8" t="n">
+      <c r="A16" s="7" t="n">
         <v>12</v>
       </c>
-      <c r="B16" s="9" t="inlineStr">
+      <c r="B16" s="8" t="inlineStr">
         <is>
           <t>HOMMER--MAHU</t>
         </is>
       </c>
-      <c r="C16" s="10" t="inlineStr">
+      <c r="C16" s="9" t="inlineStr">
         <is>
           <t>Louis</t>
         </is>
       </c>
-      <c r="D16" s="10" t="inlineStr">
+      <c r="D16" s="9" t="inlineStr">
         <is>
           <t>Energetics bleu</t>
         </is>
       </c>
-      <c r="E16" s="10" t="inlineStr">
+      <c r="E16" s="9" t="inlineStr">
         <is>
           <t>Asics orange/bleu</t>
         </is>
       </c>
-      <c r="F16" s="10" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="4" t="n">
@@ -3303,33 +3097,31 @@
           <t>Skechers bleu</t>
         </is>
       </c>
-      <c r="F17" s="6" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="8" t="n">
+      <c r="A18" s="7" t="n">
         <v>14</v>
       </c>
-      <c r="B18" s="9" t="inlineStr">
+      <c r="B18" s="8" t="inlineStr">
         <is>
           <t>LEGRAND</t>
         </is>
       </c>
-      <c r="C18" s="10" t="inlineStr">
+      <c r="C18" s="9" t="inlineStr">
         <is>
           <t>Valentin</t>
         </is>
       </c>
-      <c r="D18" s="10" t="inlineStr">
+      <c r="D18" s="9" t="inlineStr">
         <is>
           <t>Kalenji noir</t>
         </is>
       </c>
-      <c r="E18" s="10" t="inlineStr">
+      <c r="E18" s="9" t="inlineStr">
         <is>
           <t>In Extenso noir</t>
         </is>
       </c>
-      <c r="F18" s="10" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="4" t="n">
@@ -3355,33 +3147,31 @@
           <t>Asics bleu</t>
         </is>
       </c>
-      <c r="F19" s="6" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="8" t="n">
+      <c r="A20" s="7" t="n">
         <v>16</v>
       </c>
-      <c r="B20" s="9" t="inlineStr">
+      <c r="B20" s="8" t="inlineStr">
         <is>
           <t>LEVERT</t>
         </is>
       </c>
-      <c r="C20" s="10" t="inlineStr">
+      <c r="C20" s="9" t="inlineStr">
         <is>
           <t>Quentin</t>
         </is>
       </c>
-      <c r="D20" s="10" t="inlineStr">
+      <c r="D20" s="9" t="inlineStr">
         <is>
           <t>Asics noir</t>
         </is>
       </c>
-      <c r="E20" s="10" t="inlineStr">
+      <c r="E20" s="9" t="inlineStr">
         <is>
           <t>Brooks noir</t>
         </is>
       </c>
-      <c r="F20" s="10" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="4" t="n">
@@ -3407,33 +3197,31 @@
           <t>Diadora rouge</t>
         </is>
       </c>
-      <c r="F21" s="6" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="8" t="n">
+      <c r="A22" s="7" t="n">
         <v>18</v>
       </c>
-      <c r="B22" s="9" t="inlineStr">
+      <c r="B22" s="8" t="inlineStr">
         <is>
           <t>REBOUT</t>
         </is>
       </c>
-      <c r="C22" s="10" t="inlineStr">
+      <c r="C22" s="9" t="inlineStr">
         <is>
           <t>Cyrielle</t>
         </is>
       </c>
-      <c r="D22" s="10" t="inlineStr">
+      <c r="D22" s="9" t="inlineStr">
         <is>
           <t>Kalenji noir/rose</t>
         </is>
       </c>
-      <c r="E22" s="10" t="inlineStr">
+      <c r="E22" s="9" t="inlineStr">
         <is>
           <t>Kiprun noir</t>
         </is>
       </c>
-      <c r="F22" s="10" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="4" t="n">
@@ -3459,33 +3247,31 @@
           <t>Unyk noir</t>
         </is>
       </c>
-      <c r="F23" s="6" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="8" t="n">
+      <c r="A24" s="7" t="n">
         <v>20</v>
       </c>
-      <c r="B24" s="9" t="inlineStr">
+      <c r="B24" s="8" t="inlineStr">
         <is>
           <t>TEMPEZ</t>
         </is>
       </c>
-      <c r="C24" s="10" t="inlineStr">
+      <c r="C24" s="9" t="inlineStr">
         <is>
           <t>Antoine</t>
         </is>
       </c>
-      <c r="D24" s="10" t="inlineStr">
+      <c r="D24" s="9" t="inlineStr">
         <is>
           <t>Babolat blanche</t>
         </is>
       </c>
-      <c r="E24" s="10" t="inlineStr">
+      <c r="E24" s="9" t="inlineStr">
         <is>
           <t>Asics bleu</t>
         </is>
       </c>
-      <c r="F24" s="10" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="4" t="n">
@@ -3511,33 +3297,31 @@
           <t>Kalenji bleu</t>
         </is>
       </c>
-      <c r="F25" s="6" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="8" t="n">
+      <c r="A26" s="7" t="n">
         <v>22</v>
       </c>
-      <c r="B26" s="9" t="inlineStr">
+      <c r="B26" s="8" t="inlineStr">
         <is>
           <t>VALCKE</t>
         </is>
       </c>
-      <c r="C26" s="10" t="inlineStr">
+      <c r="C26" s="9" t="inlineStr">
         <is>
           <t>Mathis</t>
         </is>
       </c>
-      <c r="D26" s="10" t="inlineStr">
+      <c r="D26" s="9" t="inlineStr">
         <is>
           <t>1005 bleu</t>
         </is>
       </c>
-      <c r="E26" s="10" t="inlineStr">
+      <c r="E26" s="9" t="inlineStr">
         <is>
           <t>Asics noir/bleu</t>
         </is>
       </c>
-      <c r="F26" s="10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3550,7 +3334,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F33"/>
+  <dimension ref="A1:E33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -3558,7 +3342,6 @@
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="26" customWidth="1" min="4" max="4"/>
     <col width="26" customWidth="1" min="5" max="5"/>
-    <col width="48" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3571,7 +3354,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Case orange = paire inventée (reprise d'une autre paire de la liste)  ·  Case grise = dispensé</t>
+          <t>Case grise = dispensé</t>
         </is>
       </c>
     </row>
@@ -3599,11 +3382,6 @@
       <c r="E4" s="3" t="inlineStr">
         <is>
           <t>Baskets extérieur</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>Remarque</t>
         </is>
       </c>
     </row>
@@ -3631,33 +3409,31 @@
           <t>Adidas bleu</t>
         </is>
       </c>
-      <c r="F5" s="6" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="8" t="n">
+      <c r="A6" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="9" t="inlineStr">
+      <c r="B6" s="8" t="inlineStr">
         <is>
           <t>BRIOIS</t>
         </is>
       </c>
-      <c r="C6" s="10" t="inlineStr">
+      <c r="C6" s="9" t="inlineStr">
         <is>
           <t>Louis</t>
         </is>
       </c>
-      <c r="D6" s="10" t="inlineStr">
+      <c r="D6" s="9" t="inlineStr">
         <is>
           <t>Adidas noir/blanc</t>
         </is>
       </c>
-      <c r="E6" s="10" t="inlineStr">
+      <c r="E6" s="9" t="inlineStr">
         <is>
           <t>Adidas noir &amp; blanc</t>
         </is>
       </c>
-      <c r="F6" s="10" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
@@ -3683,39 +3459,29 @@
           <t>Adidas gris/rose</t>
         </is>
       </c>
-      <c r="F7" s="6" t="inlineStr">
-        <is>
-          <t>Les 2 notées « inter » → Adidas mise en exter</t>
-        </is>
-      </c>
     </row>
     <row r="8">
-      <c r="A8" s="8" t="n">
+      <c r="A8" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="9" t="inlineStr">
+      <c r="B8" s="8" t="inlineStr">
         <is>
           <t>CREPIN</t>
         </is>
       </c>
-      <c r="C8" s="10" t="inlineStr">
+      <c r="C8" s="9" t="inlineStr">
         <is>
           <t>Marceau</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="D8" s="9" t="inlineStr">
         <is>
           <t>Umbro noir</t>
         </is>
       </c>
-      <c r="E8" s="7" t="inlineStr">
+      <c r="E8" s="9" t="inlineStr">
         <is>
           <t>Adidas noir</t>
-        </is>
-      </c>
-      <c r="F8" s="10" t="inlineStr">
-        <is>
-          <t>Inventé : inter + exter</t>
         </is>
       </c>
     </row>
@@ -3743,37 +3509,31 @@
           <t>Asics noir/vert</t>
         </is>
       </c>
-      <c r="F9" s="6" t="inlineStr">
-        <is>
-          <t>Les 2 notées « inter » → Asics mise en exter</t>
-        </is>
-      </c>
     </row>
     <row r="10">
-      <c r="A10" s="8" t="n">
+      <c r="A10" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="9" t="inlineStr">
+      <c r="B10" s="8" t="inlineStr">
         <is>
           <t>DEJARDIN</t>
         </is>
       </c>
-      <c r="C10" s="10" t="inlineStr">
+      <c r="C10" s="9" t="inlineStr">
         <is>
           <t>Killian</t>
         </is>
       </c>
-      <c r="D10" s="10" t="inlineStr">
+      <c r="D10" s="9" t="inlineStr">
         <is>
           <t>Unyk noir</t>
         </is>
       </c>
-      <c r="E10" s="10" t="inlineStr">
+      <c r="E10" s="9" t="inlineStr">
         <is>
           <t>Unyk gris/noir</t>
         </is>
       </c>
-      <c r="F10" s="10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
@@ -3799,33 +3559,31 @@
           <t>Nike noir</t>
         </is>
       </c>
-      <c r="F11" s="6" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="8" t="n">
+      <c r="A12" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="B12" s="9" t="inlineStr">
+      <c r="B12" s="8" t="inlineStr">
         <is>
           <t>DELAVENNE</t>
         </is>
       </c>
-      <c r="C12" s="10" t="inlineStr">
+      <c r="C12" s="9" t="inlineStr">
         <is>
           <t>Mathis</t>
         </is>
       </c>
-      <c r="D12" s="10" t="inlineStr">
+      <c r="D12" s="9" t="inlineStr">
         <is>
           <t>Asics noir</t>
         </is>
       </c>
-      <c r="E12" s="10" t="inlineStr">
+      <c r="E12" s="9" t="inlineStr">
         <is>
           <t>Adidas noir</t>
         </is>
       </c>
-      <c r="F12" s="10" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
@@ -3851,33 +3609,31 @@
           <t>Nike noir</t>
         </is>
       </c>
-      <c r="F13" s="6" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="8" t="n">
+      <c r="A14" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="B14" s="9" t="inlineStr">
+      <c r="B14" s="8" t="inlineStr">
         <is>
           <t>DESCAMPS</t>
         </is>
       </c>
-      <c r="C14" s="10" t="inlineStr">
+      <c r="C14" s="9" t="inlineStr">
         <is>
           <t>Jules</t>
         </is>
       </c>
-      <c r="D14" s="10" t="inlineStr">
+      <c r="D14" s="9" t="inlineStr">
         <is>
           <t>Nike noir</t>
         </is>
       </c>
-      <c r="E14" s="10" t="inlineStr">
+      <c r="E14" s="9" t="inlineStr">
         <is>
           <t>NB bleu</t>
         </is>
       </c>
-      <c r="F14" s="10" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
@@ -3903,33 +3659,31 @@
           <t>Nike rose &amp; noir</t>
         </is>
       </c>
-      <c r="F15" s="6" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="8" t="n">
+      <c r="A16" s="7" t="n">
         <v>12</v>
       </c>
-      <c r="B16" s="9" t="inlineStr">
+      <c r="B16" s="8" t="inlineStr">
         <is>
           <t>DUBREUIL</t>
         </is>
       </c>
-      <c r="C16" s="10" t="inlineStr">
+      <c r="C16" s="9" t="inlineStr">
         <is>
           <t>Grégoire</t>
         </is>
       </c>
-      <c r="D16" s="10" t="inlineStr">
+      <c r="D16" s="9" t="inlineStr">
         <is>
           <t>Kalenji bleu</t>
         </is>
       </c>
-      <c r="E16" s="10" t="inlineStr">
+      <c r="E16" s="9" t="inlineStr">
         <is>
           <t>Kalenji noir</t>
         </is>
       </c>
-      <c r="F16" s="10" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="4" t="n">
@@ -3955,33 +3709,31 @@
           <t>Nike bleu &amp; rose</t>
         </is>
       </c>
-      <c r="F17" s="6" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="8" t="n">
+      <c r="A18" s="7" t="n">
         <v>14</v>
       </c>
-      <c r="B18" s="9" t="inlineStr">
+      <c r="B18" s="8" t="inlineStr">
         <is>
           <t>DUHAMEL</t>
         </is>
       </c>
-      <c r="C18" s="10" t="inlineStr">
+      <c r="C18" s="9" t="inlineStr">
         <is>
           <t>Capucine</t>
         </is>
       </c>
-      <c r="D18" s="10" t="inlineStr">
+      <c r="D18" s="9" t="inlineStr">
         <is>
           <t>Adidas blanche</t>
         </is>
       </c>
-      <c r="E18" s="10" t="inlineStr">
+      <c r="E18" s="9" t="inlineStr">
         <is>
           <t>Asics noir</t>
         </is>
       </c>
-      <c r="F18" s="10" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="4" t="n">
@@ -4007,33 +3759,31 @@
           <t>Unyk bleu &amp; rouge</t>
         </is>
       </c>
-      <c r="F19" s="6" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="8" t="n">
+      <c r="A20" s="7" t="n">
         <v>16</v>
       </c>
-      <c r="B20" s="9" t="inlineStr">
+      <c r="B20" s="8" t="inlineStr">
         <is>
           <t>JORANT</t>
         </is>
       </c>
-      <c r="C20" s="10" t="inlineStr">
+      <c r="C20" s="9" t="inlineStr">
         <is>
           <t>Mathéo</t>
         </is>
       </c>
-      <c r="D20" s="10" t="inlineStr">
+      <c r="D20" s="9" t="inlineStr">
         <is>
           <t>Adidas blanc &amp; bleu</t>
         </is>
       </c>
-      <c r="E20" s="10" t="inlineStr">
+      <c r="E20" s="9" t="inlineStr">
         <is>
           <t>Nike noir</t>
         </is>
       </c>
-      <c r="F20" s="10" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="4" t="n">
@@ -4059,33 +3809,31 @@
           <t>Kalenji bleu</t>
         </is>
       </c>
-      <c r="F21" s="6" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="8" t="n">
+      <c r="A22" s="7" t="n">
         <v>18</v>
       </c>
-      <c r="B22" s="9" t="inlineStr">
+      <c r="B22" s="8" t="inlineStr">
         <is>
           <t>LEFEVRE</t>
         </is>
       </c>
-      <c r="C22" s="10" t="inlineStr">
+      <c r="C22" s="9" t="inlineStr">
         <is>
           <t>Manon</t>
         </is>
       </c>
-      <c r="D22" s="10" t="inlineStr">
+      <c r="D22" s="9" t="inlineStr">
         <is>
           <t>Nike violet/noir</t>
         </is>
       </c>
-      <c r="E22" s="10" t="inlineStr">
+      <c r="E22" s="9" t="inlineStr">
         <is>
           <t>Adidas rose &amp; noir</t>
         </is>
       </c>
-      <c r="F22" s="10" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="4" t="n">
@@ -4111,33 +3859,31 @@
           <t>Nike noir</t>
         </is>
       </c>
-      <c r="F23" s="6" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="8" t="n">
+      <c r="A24" s="7" t="n">
         <v>20</v>
       </c>
-      <c r="B24" s="9" t="inlineStr">
+      <c r="B24" s="8" t="inlineStr">
         <is>
           <t>MARECHAL</t>
         </is>
       </c>
-      <c r="C24" s="10" t="inlineStr">
+      <c r="C24" s="9" t="inlineStr">
         <is>
           <t>Alexandre</t>
         </is>
       </c>
-      <c r="D24" s="10" t="inlineStr">
+      <c r="D24" s="9" t="inlineStr">
         <is>
           <t>Asics bleu</t>
         </is>
       </c>
-      <c r="E24" s="10" t="inlineStr">
+      <c r="E24" s="9" t="inlineStr">
         <is>
           <t>Adidas noir</t>
         </is>
       </c>
-      <c r="F24" s="10" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="4" t="n">
@@ -4163,33 +3909,31 @@
           <t>Asics bleu power</t>
         </is>
       </c>
-      <c r="F25" s="6" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="8" t="n">
+      <c r="A26" s="7" t="n">
         <v>22</v>
       </c>
-      <c r="B26" s="9" t="inlineStr">
+      <c r="B26" s="8" t="inlineStr">
         <is>
           <t>POUTRAIN</t>
         </is>
       </c>
-      <c r="C26" s="10" t="inlineStr">
+      <c r="C26" s="9" t="inlineStr">
         <is>
           <t>Alexis</t>
         </is>
       </c>
-      <c r="D26" s="10" t="inlineStr">
+      <c r="D26" s="9" t="inlineStr">
         <is>
           <t>Asics noir &amp; bleu</t>
         </is>
       </c>
-      <c r="E26" s="10" t="inlineStr">
+      <c r="E26" s="9" t="inlineStr">
         <is>
           <t>Asics noir</t>
         </is>
       </c>
-      <c r="F26" s="10" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="4" t="n">
@@ -4215,33 +3959,31 @@
           <t>Nike blanche</t>
         </is>
       </c>
-      <c r="F27" s="6" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="8" t="n">
+      <c r="A28" s="7" t="n">
         <v>24</v>
       </c>
-      <c r="B28" s="9" t="inlineStr">
+      <c r="B28" s="8" t="inlineStr">
         <is>
           <t>ROEDOLF</t>
         </is>
       </c>
-      <c r="C28" s="10" t="inlineStr">
+      <c r="C28" s="9" t="inlineStr">
         <is>
           <t>Erwan</t>
         </is>
       </c>
-      <c r="D28" s="10" t="inlineStr">
+      <c r="D28" s="9" t="inlineStr">
         <is>
           <t>Puma noir &amp; orange</t>
         </is>
       </c>
-      <c r="E28" s="10" t="inlineStr">
+      <c r="E28" s="9" t="inlineStr">
         <is>
           <t>Asics bleu</t>
         </is>
       </c>
-      <c r="F28" s="10" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="4" t="n">
@@ -4267,35 +4009,29 @@
           <t>Asics noir</t>
         </is>
       </c>
-      <c r="F29" s="6" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="8" t="n">
+      <c r="A30" s="7" t="n">
         <v>26</v>
       </c>
-      <c r="B30" s="9" t="inlineStr">
+      <c r="B30" s="8" t="inlineStr">
         <is>
           <t>SENECHAL</t>
         </is>
       </c>
-      <c r="C30" s="10" t="inlineStr">
+      <c r="C30" s="9" t="inlineStr">
         <is>
           <t>Léonie</t>
         </is>
       </c>
-      <c r="D30" s="10" t="inlineStr">
+      <c r="D30" s="9" t="inlineStr">
         <is>
           <t>Adidas kaki</t>
         </is>
       </c>
-      <c r="E30" s="10" t="inlineStr">
+      <c r="E30" s="9" t="inlineStr">
         <is>
           <t>Asics noir</t>
-        </is>
-      </c>
-      <c r="F30" s="10" t="inlineStr">
-        <is>
-          <t>Asics : inter/exter non précisé</t>
         </is>
       </c>
     </row>
@@ -4318,42 +4054,36 @@
           <t>Asics noir/violet</t>
         </is>
       </c>
-      <c r="E31" s="7" t="inlineStr">
+      <c r="E31" s="6" t="inlineStr">
         <is>
           <t>Unyk noir</t>
         </is>
       </c>
-      <c r="F31" s="6" t="inlineStr">
-        <is>
-          <t>Asics : inter/exter non précisé; Inventé : exter</t>
-        </is>
-      </c>
     </row>
     <row r="32">
-      <c r="A32" s="8" t="n">
+      <c r="A32" s="7" t="n">
         <v>28</v>
       </c>
-      <c r="B32" s="9" t="inlineStr">
+      <c r="B32" s="8" t="inlineStr">
         <is>
           <t>TABARY</t>
         </is>
       </c>
-      <c r="C32" s="10" t="inlineStr">
+      <c r="C32" s="9" t="inlineStr">
         <is>
           <t>Judith</t>
         </is>
       </c>
-      <c r="D32" s="10" t="inlineStr">
+      <c r="D32" s="9" t="inlineStr">
         <is>
           <t>Kiprun bleu ciel</t>
         </is>
       </c>
-      <c r="E32" s="10" t="inlineStr">
+      <c r="E32" s="9" t="inlineStr">
         <is>
           <t>Nike blanche</t>
         </is>
       </c>
-      <c r="F32" s="10" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="4" t="n">
@@ -4379,7 +4109,6 @@
           <t>Kalenji noir</t>
         </is>
       </c>
-      <c r="F33" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4392,7 +4121,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:E26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -4400,7 +4129,6 @@
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="26" customWidth="1" min="4" max="4"/>
     <col width="26" customWidth="1" min="5" max="5"/>
-    <col width="48" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4413,7 +4141,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Case orange = paire inventée (reprise d'une autre paire de la liste)  ·  Case grise = dispensé</t>
+          <t>Case grise = dispensé</t>
         </is>
       </c>
     </row>
@@ -4441,11 +4169,6 @@
       <c r="E4" s="3" t="inlineStr">
         <is>
           <t>Baskets extérieur</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>Remarque</t>
         </is>
       </c>
     </row>
@@ -4473,33 +4196,31 @@
           <t>Adidas bleu</t>
         </is>
       </c>
-      <c r="F5" s="6" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="8" t="n">
+      <c r="A6" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="9" t="inlineStr">
+      <c r="B6" s="8" t="inlineStr">
         <is>
           <t>ASSELIN</t>
         </is>
       </c>
-      <c r="C6" s="10" t="inlineStr">
+      <c r="C6" s="9" t="inlineStr">
         <is>
           <t>Maxence</t>
         </is>
       </c>
-      <c r="D6" s="10" t="inlineStr">
+      <c r="D6" s="9" t="inlineStr">
         <is>
           <t>Adidas blanche</t>
         </is>
       </c>
-      <c r="E6" s="10" t="inlineStr">
+      <c r="E6" s="9" t="inlineStr">
         <is>
           <t>Adidas noir</t>
         </is>
       </c>
-      <c r="F6" s="10" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
@@ -4525,33 +4246,31 @@
           <t>Kiprun bleu</t>
         </is>
       </c>
-      <c r="F7" s="6" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="8" t="n">
+      <c r="A8" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="9" t="inlineStr">
+      <c r="B8" s="8" t="inlineStr">
         <is>
           <t>BERTOUX</t>
         </is>
       </c>
-      <c r="C8" s="10" t="inlineStr">
+      <c r="C8" s="9" t="inlineStr">
         <is>
           <t>Jules</t>
         </is>
       </c>
-      <c r="D8" s="10" t="inlineStr">
+      <c r="D8" s="9" t="inlineStr">
         <is>
           <t>Nike blanche</t>
         </is>
       </c>
-      <c r="E8" s="10" t="inlineStr">
+      <c r="E8" s="9" t="inlineStr">
         <is>
           <t>Nike noir</t>
         </is>
       </c>
-      <c r="F8" s="10" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
@@ -4567,49 +4286,39 @@
           <t>Romain</t>
         </is>
       </c>
-      <c r="D9" s="7" t="inlineStr">
+      <c r="D9" s="6" t="inlineStr">
         <is>
           <t>Asics blanche</t>
         </is>
       </c>
-      <c r="E9" s="7" t="inlineStr">
+      <c r="E9" s="6" t="inlineStr">
         <is>
           <t>Adidas noir/bleu</t>
         </is>
       </c>
-      <c r="F9" s="6" t="inlineStr">
-        <is>
-          <t>Inventé : inter + exter</t>
-        </is>
-      </c>
     </row>
     <row r="10">
-      <c r="A10" s="8" t="n">
+      <c r="A10" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="9" t="inlineStr">
+      <c r="B10" s="8" t="inlineStr">
         <is>
           <t>CAMUS</t>
         </is>
       </c>
-      <c r="C10" s="10" t="inlineStr">
+      <c r="C10" s="9" t="inlineStr">
         <is>
           <t>Pierre</t>
         </is>
       </c>
-      <c r="D10" s="10" t="inlineStr">
+      <c r="D10" s="9" t="inlineStr">
         <is>
           <t>Asics bleu/orange</t>
         </is>
       </c>
-      <c r="E10" s="7" t="inlineStr">
+      <c r="E10" s="9" t="inlineStr">
         <is>
           <t>Kalenji gris</t>
-        </is>
-      </c>
-      <c r="F10" s="10" t="inlineStr">
-        <is>
-          <t>Inventé : exter</t>
         </is>
       </c>
     </row>
@@ -4627,49 +4336,39 @@
           <t>Jules</t>
         </is>
       </c>
-      <c r="D11" s="7" t="inlineStr">
+      <c r="D11" s="6" t="inlineStr">
         <is>
           <t>Adidas beige</t>
         </is>
       </c>
-      <c r="E11" s="7" t="inlineStr">
+      <c r="E11" s="6" t="inlineStr">
         <is>
           <t>Adidas bleu marine</t>
         </is>
       </c>
-      <c r="F11" s="6" t="inlineStr">
-        <is>
-          <t>Inventé : inter + exter</t>
-        </is>
-      </c>
     </row>
     <row r="12">
-      <c r="A12" s="8" t="n">
+      <c r="A12" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="B12" s="9" t="inlineStr">
+      <c r="B12" s="8" t="inlineStr">
         <is>
           <t>COMBLE</t>
         </is>
       </c>
-      <c r="C12" s="10" t="inlineStr">
+      <c r="C12" s="9" t="inlineStr">
         <is>
           <t>Pierre</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="D12" s="9" t="inlineStr">
         <is>
           <t>Kalenji noir/rose</t>
         </is>
       </c>
-      <c r="E12" s="7" t="inlineStr">
+      <c r="E12" s="9" t="inlineStr">
         <is>
           <t>Nike gris/orange</t>
-        </is>
-      </c>
-      <c r="F12" s="10" t="inlineStr">
-        <is>
-          <t>Inventé : inter + exter</t>
         </is>
       </c>
     </row>
@@ -4692,44 +4391,34 @@
           <t>Adidas beige</t>
         </is>
       </c>
-      <c r="E13" s="7" t="inlineStr">
+      <c r="E13" s="6" t="inlineStr">
         <is>
           <t>Kalenji noir</t>
         </is>
       </c>
-      <c r="F13" s="6" t="inlineStr">
-        <is>
-          <t>Inventé : exter</t>
-        </is>
-      </c>
     </row>
     <row r="14">
-      <c r="A14" s="8" t="n">
+      <c r="A14" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="B14" s="9" t="inlineStr">
+      <c r="B14" s="8" t="inlineStr">
         <is>
           <t>CORNILLE</t>
         </is>
       </c>
-      <c r="C14" s="10" t="inlineStr">
+      <c r="C14" s="9" t="inlineStr">
         <is>
           <t>Manon</t>
         </is>
       </c>
-      <c r="D14" s="7" t="inlineStr">
+      <c r="D14" s="9" t="inlineStr">
         <is>
           <t>Asics bleu/noir</t>
         </is>
       </c>
-      <c r="E14" s="7" t="inlineStr">
+      <c r="E14" s="9" t="inlineStr">
         <is>
           <t>Adidas bleu</t>
-        </is>
-      </c>
-      <c r="F14" s="10" t="inlineStr">
-        <is>
-          <t>Inventé : inter + exter</t>
         </is>
       </c>
     </row>
@@ -4747,7 +4436,7 @@
           <t>Maxime</t>
         </is>
       </c>
-      <c r="D15" s="7" t="inlineStr">
+      <c r="D15" s="6" t="inlineStr">
         <is>
           <t>Kalenji noir</t>
         </is>
@@ -4757,39 +4446,29 @@
           <t>Nike noir</t>
         </is>
       </c>
-      <c r="F15" s="6" t="inlineStr">
-        <is>
-          <t>Inventé : inter</t>
-        </is>
-      </c>
     </row>
     <row r="16">
-      <c r="A16" s="8" t="n">
+      <c r="A16" s="7" t="n">
         <v>12</v>
       </c>
-      <c r="B16" s="9" t="inlineStr">
+      <c r="B16" s="8" t="inlineStr">
         <is>
           <t>DEVILLE</t>
         </is>
       </c>
-      <c r="C16" s="10" t="inlineStr">
+      <c r="C16" s="9" t="inlineStr">
         <is>
           <t>Oscar</t>
         </is>
       </c>
-      <c r="D16" s="7" t="inlineStr">
+      <c r="D16" s="9" t="inlineStr">
         <is>
           <t>Kalenji gris</t>
         </is>
       </c>
-      <c r="E16" s="7" t="inlineStr">
+      <c r="E16" s="9" t="inlineStr">
         <is>
           <t>Adidas blanc/violet</t>
-        </is>
-      </c>
-      <c r="F16" s="10" t="inlineStr">
-        <is>
-          <t>Inventé : inter + exter</t>
         </is>
       </c>
     </row>
@@ -4807,49 +4486,39 @@
           <t>Marc-Antoine</t>
         </is>
       </c>
-      <c r="D17" s="7" t="inlineStr">
+      <c r="D17" s="6" t="inlineStr">
         <is>
           <t>Puma noir</t>
         </is>
       </c>
-      <c r="E17" s="7" t="inlineStr">
+      <c r="E17" s="6" t="inlineStr">
         <is>
           <t>Asics noir</t>
         </is>
       </c>
-      <c r="F17" s="6" t="inlineStr">
-        <is>
-          <t>Inventé : inter + exter</t>
-        </is>
-      </c>
     </row>
     <row r="18">
-      <c r="A18" s="8" t="n">
+      <c r="A18" s="7" t="n">
         <v>14</v>
       </c>
-      <c r="B18" s="9" t="inlineStr">
+      <c r="B18" s="8" t="inlineStr">
         <is>
           <t>GAUTHIER</t>
         </is>
       </c>
-      <c r="C18" s="10" t="inlineStr">
+      <c r="C18" s="9" t="inlineStr">
         <is>
           <t>Lucas</t>
         </is>
       </c>
-      <c r="D18" s="10" t="inlineStr">
+      <c r="D18" s="9" t="inlineStr">
         <is>
           <t>Adidas noir</t>
         </is>
       </c>
-      <c r="E18" s="7" t="inlineStr">
+      <c r="E18" s="9" t="inlineStr">
         <is>
           <t>In Extenso noir</t>
-        </is>
-      </c>
-      <c r="F18" s="10" t="inlineStr">
-        <is>
-          <t>Inventé : exter</t>
         </is>
       </c>
     </row>
@@ -4867,49 +4536,39 @@
           <t>Mathéo</t>
         </is>
       </c>
-      <c r="D19" s="7" t="inlineStr">
+      <c r="D19" s="6" t="inlineStr">
         <is>
           <t>Asics noir</t>
         </is>
       </c>
-      <c r="E19" s="7" t="inlineStr">
+      <c r="E19" s="6" t="inlineStr">
         <is>
           <t>Kalenji noir/vert</t>
         </is>
       </c>
-      <c r="F19" s="6" t="inlineStr">
-        <is>
-          <t>Absent de ta liste; Inventé : inter + exter</t>
-        </is>
-      </c>
     </row>
     <row r="20">
-      <c r="A20" s="8" t="n">
+      <c r="A20" s="7" t="n">
         <v>16</v>
       </c>
-      <c r="B20" s="9" t="inlineStr">
+      <c r="B20" s="8" t="inlineStr">
         <is>
           <t>LAGACHE</t>
         </is>
       </c>
-      <c r="C20" s="10" t="inlineStr">
+      <c r="C20" s="9" t="inlineStr">
         <is>
           <t>Coraline</t>
         </is>
       </c>
-      <c r="D20" s="7" t="inlineStr">
+      <c r="D20" s="9" t="inlineStr">
         <is>
           <t>Asics gris</t>
         </is>
       </c>
-      <c r="E20" s="10" t="inlineStr">
+      <c r="E20" s="9" t="inlineStr">
         <is>
           <t>Adidas blanc/violet</t>
-        </is>
-      </c>
-      <c r="F20" s="10" t="inlineStr">
-        <is>
-          <t>Inventé : inter</t>
         </is>
       </c>
     </row>
@@ -4937,35 +4596,29 @@
           <t>Adidas noir</t>
         </is>
       </c>
-      <c r="F21" s="6" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="8" t="n">
+      <c r="A22" s="7" t="n">
         <v>18</v>
       </c>
-      <c r="B22" s="9" t="inlineStr">
+      <c r="B22" s="8" t="inlineStr">
         <is>
           <t>MERIEAU</t>
         </is>
       </c>
-      <c r="C22" s="10" t="inlineStr">
+      <c r="C22" s="9" t="inlineStr">
         <is>
           <t>Axel</t>
         </is>
       </c>
-      <c r="D22" s="10" t="inlineStr">
+      <c r="D22" s="9" t="inlineStr">
         <is>
           <t>Airness bleu</t>
         </is>
       </c>
-      <c r="E22" s="7" t="inlineStr">
+      <c r="E22" s="9" t="inlineStr">
         <is>
           <t>Nike bleu</t>
-        </is>
-      </c>
-      <c r="F22" s="10" t="inlineStr">
-        <is>
-          <t>Airness : inter/exter non précisé; Inventé : exter</t>
         </is>
       </c>
     </row>
@@ -4983,7 +4636,7 @@
           <t>Victor</t>
         </is>
       </c>
-      <c r="D23" s="7" t="inlineStr">
+      <c r="D23" s="6" t="inlineStr">
         <is>
           <t>Asics blanche</t>
         </is>
@@ -4993,39 +4646,29 @@
           <t>Nike noir/jaune</t>
         </is>
       </c>
-      <c r="F23" s="6" t="inlineStr">
-        <is>
-          <t>Inventé : inter</t>
-        </is>
-      </c>
     </row>
     <row r="24">
-      <c r="A24" s="8" t="n">
+      <c r="A24" s="7" t="n">
         <v>20</v>
       </c>
-      <c r="B24" s="9" t="inlineStr">
+      <c r="B24" s="8" t="inlineStr">
         <is>
           <t>VALET</t>
         </is>
       </c>
-      <c r="C24" s="10" t="inlineStr">
+      <c r="C24" s="9" t="inlineStr">
         <is>
           <t>Cléa</t>
         </is>
       </c>
-      <c r="D24" s="7" t="inlineStr">
+      <c r="D24" s="9" t="inlineStr">
         <is>
           <t>Adidas vert pomme</t>
         </is>
       </c>
-      <c r="E24" s="10" t="inlineStr">
+      <c r="E24" s="9" t="inlineStr">
         <is>
           <t>Nike noir</t>
-        </is>
-      </c>
-      <c r="F24" s="10" t="inlineStr">
-        <is>
-          <t>Inventé : inter</t>
         </is>
       </c>
     </row>
@@ -5043,7 +4686,7 @@
           <t>Donat</t>
         </is>
       </c>
-      <c r="D25" s="7" t="inlineStr">
+      <c r="D25" s="6" t="inlineStr">
         <is>
           <t>Kalenji bleu</t>
         </is>
@@ -5053,37 +4696,31 @@
           <t>Asics bleu</t>
         </is>
       </c>
-      <c r="F25" s="6" t="inlineStr">
-        <is>
-          <t>Inventé : inter</t>
-        </is>
-      </c>
     </row>
     <row r="26">
-      <c r="A26" s="8" t="n">
+      <c r="A26" s="7" t="n">
         <v>22</v>
       </c>
-      <c r="B26" s="9" t="inlineStr">
+      <c r="B26" s="8" t="inlineStr">
         <is>
           <t>VIGNE--PLAISANT</t>
         </is>
       </c>
-      <c r="C26" s="10" t="inlineStr">
+      <c r="C26" s="9" t="inlineStr">
         <is>
           <t>Marius</t>
         </is>
       </c>
-      <c r="D26" s="10" t="inlineStr">
+      <c r="D26" s="9" t="inlineStr">
         <is>
           <t>Asics blanche</t>
         </is>
       </c>
-      <c r="E26" s="10" t="inlineStr">
+      <c r="E26" s="9" t="inlineStr">
         <is>
           <t>Adidas noir/gris/jaune</t>
         </is>
       </c>
-      <c r="F26" s="10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5096,7 +4733,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:E25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -5104,7 +4741,6 @@
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="26" customWidth="1" min="4" max="4"/>
     <col width="26" customWidth="1" min="5" max="5"/>
-    <col width="48" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5117,12 +4753,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Case orange = paire inventée (reprise d'une autre paire de la liste)  ·  Case grise = dispensé</t>
+          <t>Case grise = dispensé</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="11" t="inlineStr">
+      <c r="A3" s="10" t="inlineStr">
         <is>
           <t>Rugby : 6 ou 7 séances — 6 x 3 x 500.</t>
         </is>
@@ -5152,11 +4788,6 @@
       <c r="E4" s="3" t="inlineStr">
         <is>
           <t>Baskets extérieur</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>Remarque</t>
         </is>
       </c>
     </row>
@@ -5174,47 +4805,41 @@
           <t>Benjamin</t>
         </is>
       </c>
-      <c r="D5" s="7" t="inlineStr">
+      <c r="D5" s="6" t="inlineStr">
         <is>
           <t>Adidas noir</t>
         </is>
       </c>
-      <c r="E5" s="7" t="inlineStr">
+      <c r="E5" s="6" t="inlineStr">
         <is>
           <t>Kalenji gris</t>
         </is>
       </c>
-      <c r="F5" s="6" t="inlineStr">
-        <is>
-          <t>Inventé : inter + exter</t>
-        </is>
-      </c>
     </row>
     <row r="6">
-      <c r="A6" s="8" t="n">
+      <c r="A6" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="9" t="inlineStr">
+      <c r="B6" s="8" t="inlineStr">
         <is>
           <t>BONNIERE</t>
         </is>
       </c>
-      <c r="C6" s="10" t="inlineStr">
+      <c r="C6" s="9" t="inlineStr">
         <is>
           <t>Maxime</t>
         </is>
       </c>
-      <c r="D6" s="10" t="inlineStr">
+      <c r="D6" s="9" t="inlineStr">
         <is>
           <t>Kalenji noir</t>
         </is>
       </c>
-      <c r="E6" s="10" t="inlineStr">
+      <c r="E6" s="9" t="inlineStr">
         <is>
           <t>Asics orange</t>
         </is>
       </c>
-      <c r="F6" s="10" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
@@ -5230,47 +4855,37 @@
           <t>Gabin</t>
         </is>
       </c>
-      <c r="D7" s="12" t="inlineStr">
+      <c r="D7" s="11" t="inlineStr">
         <is>
           <t>Dispensé</t>
         </is>
       </c>
-      <c r="E7" s="12" t="inlineStr">
+      <c r="E7" s="11" t="inlineStr">
         <is>
           <t>Dispensé</t>
         </is>
       </c>
-      <c r="F7" s="6" t="inlineStr">
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>BOUTILLIER</t>
+        </is>
+      </c>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>Damon</t>
+        </is>
+      </c>
+      <c r="D8" s="11" t="inlineStr">
         <is>
           <t>Dispensé</t>
         </is>
       </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="B8" s="9" t="inlineStr">
-        <is>
-          <t>BOUTILLIER</t>
-        </is>
-      </c>
-      <c r="C8" s="10" t="inlineStr">
-        <is>
-          <t>Damon</t>
-        </is>
-      </c>
-      <c r="D8" s="12" t="inlineStr">
-        <is>
-          <t>Dispensé</t>
-        </is>
-      </c>
-      <c r="E8" s="12" t="inlineStr">
-        <is>
-          <t>Dispensé</t>
-        </is>
-      </c>
-      <c r="F8" s="10" t="inlineStr">
+      <c r="E8" s="11" t="inlineStr">
         <is>
           <t>Dispensé</t>
         </is>
@@ -5300,33 +4915,31 @@
           <t>Kalenji gris</t>
         </is>
       </c>
-      <c r="F9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="8" t="n">
+      <c r="A10" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="9" t="inlineStr">
+      <c r="B10" s="8" t="inlineStr">
         <is>
           <t>DEBUREAUX</t>
         </is>
       </c>
-      <c r="C10" s="10" t="inlineStr">
+      <c r="C10" s="9" t="inlineStr">
         <is>
           <t>Alexandre</t>
         </is>
       </c>
-      <c r="D10" s="10" t="inlineStr">
+      <c r="D10" s="9" t="inlineStr">
         <is>
           <t>Kalenji gris</t>
         </is>
       </c>
-      <c r="E10" s="10" t="inlineStr">
+      <c r="E10" s="9" t="inlineStr">
         <is>
           <t>Kalenji gris &amp; noir</t>
         </is>
       </c>
-      <c r="F10" s="10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
@@ -5342,49 +4955,39 @@
           <t>Raphaël</t>
         </is>
       </c>
-      <c r="D11" s="7" t="inlineStr">
+      <c r="D11" s="6" t="inlineStr">
         <is>
           <t>Unyk noir/bleu</t>
         </is>
       </c>
-      <c r="E11" s="7" t="inlineStr">
+      <c r="E11" s="6" t="inlineStr">
         <is>
           <t>Kalenji gris/vert</t>
         </is>
       </c>
-      <c r="F11" s="6" t="inlineStr">
-        <is>
-          <t>Inventé : inter + exter</t>
-        </is>
-      </c>
     </row>
     <row r="12">
-      <c r="A12" s="8" t="n">
+      <c r="A12" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="B12" s="9" t="inlineStr">
+      <c r="B12" s="8" t="inlineStr">
         <is>
           <t>DEROME</t>
         </is>
       </c>
-      <c r="C12" s="10" t="inlineStr">
+      <c r="C12" s="9" t="inlineStr">
         <is>
           <t>Louane</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="D12" s="9" t="inlineStr">
         <is>
           <t>Asics noir</t>
         </is>
       </c>
-      <c r="E12" s="7" t="inlineStr">
+      <c r="E12" s="9" t="inlineStr">
         <is>
           <t>Adidas noir</t>
-        </is>
-      </c>
-      <c r="F12" s="10" t="inlineStr">
-        <is>
-          <t>Inventé : inter + exter</t>
         </is>
       </c>
     </row>
@@ -5402,49 +5005,39 @@
           <t>Thomas</t>
         </is>
       </c>
-      <c r="D13" s="7" t="inlineStr">
+      <c r="D13" s="6" t="inlineStr">
         <is>
           <t>Salomon vert</t>
         </is>
       </c>
-      <c r="E13" s="7" t="inlineStr">
+      <c r="E13" s="6" t="inlineStr">
         <is>
           <t>Kiprun noir</t>
         </is>
       </c>
-      <c r="F13" s="6" t="inlineStr">
-        <is>
-          <t>Inventé : inter + exter</t>
-        </is>
-      </c>
     </row>
     <row r="14">
-      <c r="A14" s="8" t="n">
+      <c r="A14" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="B14" s="9" t="inlineStr">
+      <c r="B14" s="8" t="inlineStr">
         <is>
           <t>FORE</t>
         </is>
       </c>
-      <c r="C14" s="10" t="inlineStr">
+      <c r="C14" s="9" t="inlineStr">
         <is>
           <t>Maxence</t>
         </is>
       </c>
-      <c r="D14" s="7" t="inlineStr">
+      <c r="D14" s="9" t="inlineStr">
         <is>
           <t>5 Miles gris</t>
         </is>
       </c>
-      <c r="E14" s="7" t="inlineStr">
+      <c r="E14" s="9" t="inlineStr">
         <is>
           <t>In Extenso bleu</t>
-        </is>
-      </c>
-      <c r="F14" s="10" t="inlineStr">
-        <is>
-          <t>Inventé : inter + exter</t>
         </is>
       </c>
     </row>
@@ -5462,47 +5055,41 @@
           <t>Tim</t>
         </is>
       </c>
-      <c r="D15" s="7" t="inlineStr">
+      <c r="D15" s="6" t="inlineStr">
         <is>
           <t>Nike blanche</t>
         </is>
       </c>
-      <c r="E15" s="7" t="inlineStr">
+      <c r="E15" s="6" t="inlineStr">
         <is>
           <t>Salomon violet</t>
         </is>
       </c>
-      <c r="F15" s="6" t="inlineStr">
-        <is>
-          <t>Inventé : inter + exter</t>
-        </is>
-      </c>
     </row>
     <row r="16">
-      <c r="A16" s="8" t="n">
+      <c r="A16" s="7" t="n">
         <v>12</v>
       </c>
-      <c r="B16" s="9" t="inlineStr">
+      <c r="B16" s="8" t="inlineStr">
         <is>
           <t>LELIEUR</t>
         </is>
       </c>
-      <c r="C16" s="10" t="inlineStr">
+      <c r="C16" s="9" t="inlineStr">
         <is>
           <t>Anthime</t>
         </is>
       </c>
-      <c r="D16" s="10" t="inlineStr">
+      <c r="D16" s="9" t="inlineStr">
         <is>
           <t>Nike noir</t>
         </is>
       </c>
-      <c r="E16" s="10" t="inlineStr">
+      <c r="E16" s="9" t="inlineStr">
         <is>
           <t>Kalenji gris</t>
         </is>
       </c>
-      <c r="F16" s="10" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="4" t="n">
@@ -5518,49 +5105,39 @@
           <t>Lilou</t>
         </is>
       </c>
-      <c r="D17" s="7" t="inlineStr">
+      <c r="D17" s="6" t="inlineStr">
         <is>
           <t>Asics bleu/noir</t>
         </is>
       </c>
-      <c r="E17" s="7" t="inlineStr">
+      <c r="E17" s="6" t="inlineStr">
         <is>
           <t>In Extenso bleu</t>
         </is>
       </c>
-      <c r="F17" s="6" t="inlineStr">
-        <is>
-          <t>Inventé : inter + exter</t>
-        </is>
-      </c>
     </row>
     <row r="18">
-      <c r="A18" s="8" t="n">
+      <c r="A18" s="7" t="n">
         <v>14</v>
       </c>
-      <c r="B18" s="9" t="inlineStr">
+      <c r="B18" s="8" t="inlineStr">
         <is>
           <t>MICHAUX PLAISANT</t>
         </is>
       </c>
-      <c r="C18" s="10" t="inlineStr">
+      <c r="C18" s="9" t="inlineStr">
         <is>
           <t>Raphaël</t>
         </is>
       </c>
-      <c r="D18" s="7" t="inlineStr">
+      <c r="D18" s="9" t="inlineStr">
         <is>
           <t>Adidas gris &amp; blanc</t>
         </is>
       </c>
-      <c r="E18" s="7" t="inlineStr">
+      <c r="E18" s="9" t="inlineStr">
         <is>
           <t>Adidas blanche</t>
-        </is>
-      </c>
-      <c r="F18" s="10" t="inlineStr">
-        <is>
-          <t>Inventé : inter + exter</t>
         </is>
       </c>
     </row>
@@ -5578,7 +5155,7 @@
           <t>Simon</t>
         </is>
       </c>
-      <c r="D19" s="7" t="inlineStr">
+      <c r="D19" s="6" t="inlineStr">
         <is>
           <t>Asics noir</t>
         </is>
@@ -5588,37 +5165,31 @@
           <t>Nike blanche</t>
         </is>
       </c>
-      <c r="F19" s="6" t="inlineStr">
-        <is>
-          <t>Inventé : inter</t>
-        </is>
-      </c>
     </row>
     <row r="20">
-      <c r="A20" s="8" t="n">
+      <c r="A20" s="7" t="n">
         <v>16</v>
       </c>
-      <c r="B20" s="9" t="inlineStr">
+      <c r="B20" s="8" t="inlineStr">
         <is>
           <t>MORREZ--FACQ</t>
         </is>
       </c>
-      <c r="C20" s="10" t="inlineStr">
+      <c r="C20" s="9" t="inlineStr">
         <is>
           <t>Juliette</t>
         </is>
       </c>
-      <c r="D20" s="10" t="inlineStr">
+      <c r="D20" s="9" t="inlineStr">
         <is>
           <t>Kalenji kaki</t>
         </is>
       </c>
-      <c r="E20" s="10" t="inlineStr">
+      <c r="E20" s="9" t="inlineStr">
         <is>
           <t>Asics bleu/orange</t>
         </is>
       </c>
-      <c r="F20" s="10" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="4" t="n">
@@ -5644,35 +5215,29 @@
           <t>Asics noir</t>
         </is>
       </c>
-      <c r="F21" s="6" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="8" t="n">
+      <c r="A22" s="7" t="n">
         <v>18</v>
       </c>
-      <c r="B22" s="9" t="inlineStr">
+      <c r="B22" s="8" t="inlineStr">
         <is>
           <t>NOREL</t>
         </is>
       </c>
-      <c r="C22" s="10" t="inlineStr">
+      <c r="C22" s="9" t="inlineStr">
         <is>
           <t>Margot</t>
         </is>
       </c>
-      <c r="D22" s="12" t="inlineStr">
+      <c r="D22" s="11" t="inlineStr">
         <is>
           <t>Dispensé</t>
         </is>
       </c>
-      <c r="E22" s="12" t="inlineStr">
+      <c r="E22" s="11" t="inlineStr">
         <is>
           <t>Dispensé</t>
-        </is>
-      </c>
-      <c r="F22" s="10" t="inlineStr">
-        <is>
-          <t>Dispensée</t>
         </is>
       </c>
     </row>
@@ -5690,7 +5255,7 @@
           <t>Matthieu</t>
         </is>
       </c>
-      <c r="D23" s="7" t="inlineStr">
+      <c r="D23" s="6" t="inlineStr">
         <is>
           <t>NB blanc/gris</t>
         </is>
@@ -5700,37 +5265,31 @@
           <t>Nike bleu/violet clair</t>
         </is>
       </c>
-      <c r="F23" s="6" t="inlineStr">
-        <is>
-          <t>Inventé : inter</t>
-        </is>
-      </c>
     </row>
     <row r="24">
-      <c r="A24" s="8" t="n">
+      <c r="A24" s="7" t="n">
         <v>20</v>
       </c>
-      <c r="B24" s="9" t="inlineStr">
+      <c r="B24" s="8" t="inlineStr">
         <is>
           <t>TABARY</t>
         </is>
       </c>
-      <c r="C24" s="10" t="inlineStr">
+      <c r="C24" s="9" t="inlineStr">
         <is>
           <t>Thibaut</t>
         </is>
       </c>
-      <c r="D24" s="10" t="inlineStr">
+      <c r="D24" s="9" t="inlineStr">
         <is>
           <t>In Extenso noir</t>
         </is>
       </c>
-      <c r="E24" s="10" t="inlineStr">
+      <c r="E24" s="9" t="inlineStr">
         <is>
           <t>In Extenso bleu</t>
         </is>
       </c>
-      <c r="F24" s="10" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="4" t="n">
@@ -5756,7 +5315,6 @@
           <t>Asics bleu</t>
         </is>
       </c>
-      <c r="F25" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5769,7 +5327,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -5777,7 +5335,6 @@
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="26" customWidth="1" min="4" max="4"/>
     <col width="26" customWidth="1" min="5" max="5"/>
-    <col width="48" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5790,12 +5347,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Case orange = paire inventée (reprise d'une autre paire de la liste)  ·  Case grise = dispensé</t>
+          <t>Case grise = dispensé</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="11" t="inlineStr">
+      <c r="A3" s="10" t="inlineStr">
         <is>
           <t>Pas de capture Ecole Directe reçue pour cette classe → noms de famille à compléter. Cycle : 12 séances /3 → 4 muscu, 4 tennis de table, 4 course d'orientation.</t>
         </is>
@@ -5825,11 +5382,6 @@
       <c r="E4" s="3" t="inlineStr">
         <is>
           <t>Baskets extérieur</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>Remarque</t>
         </is>
       </c>
     </row>
@@ -5857,39 +5409,29 @@
           <t>Kappa noir</t>
         </is>
       </c>
-      <c r="F5" s="6" t="inlineStr">
-        <is>
-          <t>Nom de famille non fourni</t>
-        </is>
-      </c>
     </row>
     <row r="6">
-      <c r="A6" s="8" t="n">
+      <c r="A6" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="9" t="inlineStr">
+      <c r="B6" s="8" t="inlineStr">
         <is>
           <t>?</t>
         </is>
       </c>
-      <c r="C6" s="10" t="inlineStr">
+      <c r="C6" s="9" t="inlineStr">
         <is>
           <t>Illan</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="D6" s="9" t="inlineStr">
         <is>
           <t>Nike noir &amp; gris</t>
         </is>
       </c>
-      <c r="E6" s="7" t="inlineStr">
+      <c r="E6" s="9" t="inlineStr">
         <is>
           <t>Asics violet</t>
-        </is>
-      </c>
-      <c r="F6" s="10" t="inlineStr">
-        <is>
-          <t>Nom de famille non fourni; Inventé : inter + exter</t>
         </is>
       </c>
     </row>
@@ -5917,39 +5459,29 @@
           <t>Adidas noir</t>
         </is>
       </c>
-      <c r="F7" s="6" t="inlineStr">
-        <is>
-          <t>Nom de famille non fourni</t>
-        </is>
-      </c>
     </row>
     <row r="8">
-      <c r="A8" s="8" t="n">
+      <c r="A8" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="9" t="inlineStr">
+      <c r="B8" s="8" t="inlineStr">
         <is>
           <t>?</t>
         </is>
       </c>
-      <c r="C8" s="10" t="inlineStr">
+      <c r="C8" s="9" t="inlineStr">
         <is>
           <t>Thibaut (1)</t>
         </is>
       </c>
-      <c r="D8" s="10" t="inlineStr">
+      <c r="D8" s="9" t="inlineStr">
         <is>
           <t>Asics bleu</t>
         </is>
       </c>
-      <c r="E8" s="7" t="inlineStr">
+      <c r="E8" s="9" t="inlineStr">
         <is>
           <t>Asics bleu</t>
-        </is>
-      </c>
-      <c r="F8" s="10" t="inlineStr">
-        <is>
-          <t>Nom de famille non fourni; Inventé : exter</t>
         </is>
       </c>
     </row>
@@ -5967,49 +5499,39 @@
           <t>Collyne</t>
         </is>
       </c>
-      <c r="D9" s="7" t="inlineStr">
+      <c r="D9" s="6" t="inlineStr">
         <is>
           <t>Nike noir &amp; gris</t>
         </is>
       </c>
-      <c r="E9" s="7" t="inlineStr">
+      <c r="E9" s="6" t="inlineStr">
         <is>
           <t>Jovas rouge</t>
         </is>
       </c>
-      <c r="F9" s="6" t="inlineStr">
-        <is>
-          <t>Nom de famille non fourni; Inventé : inter + exter</t>
-        </is>
-      </c>
     </row>
     <row r="10">
-      <c r="A10" s="8" t="n">
+      <c r="A10" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="9" t="inlineStr">
+      <c r="B10" s="8" t="inlineStr">
         <is>
           <t>?</t>
         </is>
       </c>
-      <c r="C10" s="10" t="inlineStr">
+      <c r="C10" s="9" t="inlineStr">
         <is>
           <t>Lola</t>
         </is>
       </c>
-      <c r="D10" s="10" t="inlineStr">
+      <c r="D10" s="9" t="inlineStr">
         <is>
           <t>Kalenji gris</t>
         </is>
       </c>
-      <c r="E10" s="7" t="inlineStr">
+      <c r="E10" s="9" t="inlineStr">
         <is>
           <t>Hitmark rouge</t>
-        </is>
-      </c>
-      <c r="F10" s="10" t="inlineStr">
-        <is>
-          <t>Nom de famille non fourni; Inventé : exter</t>
         </is>
       </c>
     </row>
@@ -6035,11 +5557,6 @@
       <c r="E11" s="6" t="inlineStr">
         <is>
           <t>Asics blanc/beige</t>
-        </is>
-      </c>
-      <c r="F11" s="6" t="inlineStr">
-        <is>
-          <t>Nom de famille non fourni</t>
         </is>
       </c>
     </row>
@@ -6054,7 +5571,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:E31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -6062,7 +5579,6 @@
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="26" customWidth="1" min="4" max="4"/>
     <col width="26" customWidth="1" min="5" max="5"/>
-    <col width="48" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6075,7 +5591,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Case orange = paire inventée (reprise d'une autre paire de la liste)  ·  Case grise = dispensé</t>
+          <t>Case grise = dispensé</t>
         </is>
       </c>
     </row>
@@ -6103,11 +5619,6 @@
       <c r="E4" s="3" t="inlineStr">
         <is>
           <t>Baskets extérieur</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>Remarque</t>
         </is>
       </c>
     </row>
@@ -6125,49 +5636,39 @@
           <t>Dimitri</t>
         </is>
       </c>
-      <c r="D5" s="7" t="inlineStr">
+      <c r="D5" s="6" t="inlineStr">
         <is>
           <t>Puma violet/bleu</t>
         </is>
       </c>
-      <c r="E5" s="7" t="inlineStr">
+      <c r="E5" s="6" t="inlineStr">
         <is>
           <t>Kalenji gris &amp; noir</t>
         </is>
       </c>
-      <c r="F5" s="6" t="inlineStr">
-        <is>
-          <t>Inventé : inter + exter</t>
-        </is>
-      </c>
     </row>
     <row r="6">
-      <c r="A6" s="8" t="n">
+      <c r="A6" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="9" t="inlineStr">
+      <c r="B6" s="8" t="inlineStr">
         <is>
           <t>BARTIER</t>
         </is>
       </c>
-      <c r="C6" s="10" t="inlineStr">
+      <c r="C6" s="9" t="inlineStr">
         <is>
           <t>Valentin</t>
         </is>
       </c>
-      <c r="D6" s="10" t="inlineStr">
+      <c r="D6" s="9" t="inlineStr">
         <is>
           <t>Adidas blanc/bleu</t>
         </is>
       </c>
-      <c r="E6" s="10" t="inlineStr">
+      <c r="E6" s="9" t="inlineStr">
         <is>
           <t>Asics bleu/orange</t>
-        </is>
-      </c>
-      <c r="F6" s="10" t="inlineStr">
-        <is>
-          <t>inter/exter non précisé</t>
         </is>
       </c>
     </row>
@@ -6195,33 +5696,31 @@
           <t>Kalenji noir</t>
         </is>
       </c>
-      <c r="F7" s="6" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="8" t="n">
+      <c r="A8" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="9" t="inlineStr">
+      <c r="B8" s="8" t="inlineStr">
         <is>
           <t>DACQUIN</t>
         </is>
       </c>
-      <c r="C8" s="10" t="inlineStr">
+      <c r="C8" s="9" t="inlineStr">
         <is>
           <t>Léo</t>
         </is>
       </c>
-      <c r="D8" s="10" t="inlineStr">
+      <c r="D8" s="9" t="inlineStr">
         <is>
           <t>Unyk blanche</t>
         </is>
       </c>
-      <c r="E8" s="10" t="inlineStr">
+      <c r="E8" s="9" t="inlineStr">
         <is>
           <t>Unyk noir</t>
         </is>
       </c>
-      <c r="F8" s="10" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
@@ -6247,33 +5746,31 @@
           <t>Kalenji bleu</t>
         </is>
       </c>
-      <c r="F9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="8" t="n">
+      <c r="A10" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="9" t="inlineStr">
+      <c r="B10" s="8" t="inlineStr">
         <is>
           <t>DESPATY</t>
         </is>
       </c>
-      <c r="C10" s="10" t="inlineStr">
+      <c r="C10" s="9" t="inlineStr">
         <is>
           <t>Samuel</t>
         </is>
       </c>
-      <c r="D10" s="10" t="inlineStr">
+      <c r="D10" s="9" t="inlineStr">
         <is>
           <t>Artengo blanche</t>
         </is>
       </c>
-      <c r="E10" s="10" t="inlineStr">
+      <c r="E10" s="9" t="inlineStr">
         <is>
           <t>Kalenji gris</t>
         </is>
       </c>
-      <c r="F10" s="10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
@@ -6299,35 +5796,29 @@
           <t>Nike noir</t>
         </is>
       </c>
-      <c r="F11" s="6" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="8" t="n">
+      <c r="A12" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="B12" s="9" t="inlineStr">
+      <c r="B12" s="8" t="inlineStr">
         <is>
           <t>DOUVILLE DE FRANSSU</t>
         </is>
       </c>
-      <c r="C12" s="10" t="inlineStr">
+      <c r="C12" s="9" t="inlineStr">
         <is>
           <t>Hugues</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="D12" s="9" t="inlineStr">
         <is>
           <t>Kalenji gris</t>
         </is>
       </c>
-      <c r="E12" s="7" t="inlineStr">
+      <c r="E12" s="9" t="inlineStr">
         <is>
           <t>Nike bleu/violet clair</t>
-        </is>
-      </c>
-      <c r="F12" s="10" t="inlineStr">
-        <is>
-          <t>Inventé : inter + exter</t>
         </is>
       </c>
     </row>
@@ -6355,33 +5846,31 @@
           <t>Hoka blanche</t>
         </is>
       </c>
-      <c r="F13" s="6" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="8" t="n">
+      <c r="A14" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="B14" s="9" t="inlineStr">
+      <c r="B14" s="8" t="inlineStr">
         <is>
           <t>FLEURY</t>
         </is>
       </c>
-      <c r="C14" s="10" t="inlineStr">
+      <c r="C14" s="9" t="inlineStr">
         <is>
           <t>Thibault</t>
         </is>
       </c>
-      <c r="D14" s="10" t="inlineStr">
+      <c r="D14" s="9" t="inlineStr">
         <is>
           <t>Artengo bleu marine</t>
         </is>
       </c>
-      <c r="E14" s="10" t="inlineStr">
+      <c r="E14" s="9" t="inlineStr">
         <is>
           <t>Adidas noir</t>
         </is>
       </c>
-      <c r="F14" s="10" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
@@ -6407,35 +5896,29 @@
           <t>Kalenji noir</t>
         </is>
       </c>
-      <c r="F15" s="6" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="8" t="n">
+      <c r="A16" s="7" t="n">
         <v>12</v>
       </c>
-      <c r="B16" s="9" t="inlineStr">
+      <c r="B16" s="8" t="inlineStr">
         <is>
           <t>LEMAIRE</t>
         </is>
       </c>
-      <c r="C16" s="10" t="inlineStr">
+      <c r="C16" s="9" t="inlineStr">
         <is>
           <t>Méline</t>
         </is>
       </c>
-      <c r="D16" s="7" t="inlineStr">
+      <c r="D16" s="9" t="inlineStr">
         <is>
           <t>Puma blanche</t>
         </is>
       </c>
-      <c r="E16" s="7" t="inlineStr">
+      <c r="E16" s="9" t="inlineStr">
         <is>
           <t>Nike noir/blanc</t>
-        </is>
-      </c>
-      <c r="F16" s="10" t="inlineStr">
-        <is>
-          <t>Inventé : inter + exter</t>
         </is>
       </c>
     </row>
@@ -6458,42 +5941,36 @@
           <t>Asics bleu marine</t>
         </is>
       </c>
-      <c r="E17" s="7" t="inlineStr">
+      <c r="E17" s="6" t="inlineStr">
         <is>
           <t>Adidas noir</t>
         </is>
       </c>
-      <c r="F17" s="6" t="inlineStr">
-        <is>
-          <t>Inventé : exter</t>
-        </is>
-      </c>
     </row>
     <row r="18">
-      <c r="A18" s="8" t="n">
+      <c r="A18" s="7" t="n">
         <v>14</v>
       </c>
-      <c r="B18" s="9" t="inlineStr">
+      <c r="B18" s="8" t="inlineStr">
         <is>
           <t>MARTEIN</t>
         </is>
       </c>
-      <c r="C18" s="10" t="inlineStr">
+      <c r="C18" s="9" t="inlineStr">
         <is>
           <t>Paul</t>
         </is>
       </c>
-      <c r="D18" s="10" t="inlineStr">
+      <c r="D18" s="9" t="inlineStr">
         <is>
           <t>Kalenji gris</t>
         </is>
       </c>
-      <c r="E18" s="10" t="inlineStr">
+      <c r="E18" s="9" t="inlineStr">
         <is>
           <t>Artengo blanche</t>
         </is>
       </c>
-      <c r="F18" s="10" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="4" t="n">
@@ -6514,42 +5991,36 @@
           <t>Adidas blanc/rouge</t>
         </is>
       </c>
-      <c r="E19" s="7" t="inlineStr">
+      <c r="E19" s="6" t="inlineStr">
         <is>
           <t>Artengo blanche</t>
         </is>
       </c>
-      <c r="F19" s="6" t="inlineStr">
-        <is>
-          <t>Inventé : exter</t>
-        </is>
-      </c>
     </row>
     <row r="20">
-      <c r="A20" s="8" t="n">
+      <c r="A20" s="7" t="n">
         <v>16</v>
       </c>
-      <c r="B20" s="9" t="inlineStr">
+      <c r="B20" s="8" t="inlineStr">
         <is>
           <t>PETIT</t>
         </is>
       </c>
-      <c r="C20" s="10" t="inlineStr">
+      <c r="C20" s="9" t="inlineStr">
         <is>
           <t>Jules</t>
         </is>
       </c>
-      <c r="D20" s="10" t="inlineStr">
+      <c r="D20" s="9" t="inlineStr">
         <is>
           <t>Unyk blanche</t>
         </is>
       </c>
-      <c r="E20" s="10" t="inlineStr">
+      <c r="E20" s="9" t="inlineStr">
         <is>
           <t>Unyk noir</t>
         </is>
       </c>
-      <c r="F20" s="10" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="4" t="n">
@@ -6570,42 +6041,36 @@
           <t>Kalenji bleu</t>
         </is>
       </c>
-      <c r="E21" s="7" t="inlineStr">
+      <c r="E21" s="6" t="inlineStr">
         <is>
           <t>Puma gris</t>
         </is>
       </c>
-      <c r="F21" s="6" t="inlineStr">
-        <is>
-          <t>Inventé : exter</t>
-        </is>
-      </c>
     </row>
     <row r="22">
-      <c r="A22" s="8" t="n">
+      <c r="A22" s="7" t="n">
         <v>18</v>
       </c>
-      <c r="B22" s="9" t="inlineStr">
+      <c r="B22" s="8" t="inlineStr">
         <is>
           <t>POTTIER</t>
         </is>
       </c>
-      <c r="C22" s="10" t="inlineStr">
+      <c r="C22" s="9" t="inlineStr">
         <is>
           <t>Romain</t>
         </is>
       </c>
-      <c r="D22" s="10" t="inlineStr">
+      <c r="D22" s="9" t="inlineStr">
         <is>
           <t>Unyk noir</t>
         </is>
       </c>
-      <c r="E22" s="10" t="inlineStr">
+      <c r="E22" s="9" t="inlineStr">
         <is>
           <t>Asics gris</t>
         </is>
       </c>
-      <c r="F22" s="10" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="4" t="n">
@@ -6631,35 +6096,29 @@
           <t>Kalenji bleu</t>
         </is>
       </c>
-      <c r="F23" s="6" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="8" t="n">
+      <c r="A24" s="7" t="n">
         <v>20</v>
       </c>
-      <c r="B24" s="9" t="inlineStr">
+      <c r="B24" s="8" t="inlineStr">
         <is>
           <t>SAINT-MAXENT</t>
         </is>
       </c>
-      <c r="C24" s="10" t="inlineStr">
+      <c r="C24" s="9" t="inlineStr">
         <is>
           <t>Baptiste</t>
         </is>
       </c>
-      <c r="D24" s="10" t="inlineStr">
+      <c r="D24" s="9" t="inlineStr">
         <is>
           <t>Salomon vert</t>
         </is>
       </c>
-      <c r="E24" s="7" t="inlineStr">
+      <c r="E24" s="9" t="inlineStr">
         <is>
           <t>Asics bleu</t>
-        </is>
-      </c>
-      <c r="F24" s="10" t="inlineStr">
-        <is>
-          <t>Inventé : exter</t>
         </is>
       </c>
     </row>
@@ -6687,33 +6146,31 @@
           <t>Unyk blanche</t>
         </is>
       </c>
-      <c r="F25" s="6" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="8" t="n">
+      <c r="A26" s="7" t="n">
         <v>22</v>
       </c>
-      <c r="B26" s="9" t="inlineStr">
+      <c r="B26" s="8" t="inlineStr">
         <is>
           <t>SCHAWANN</t>
         </is>
       </c>
-      <c r="C26" s="10" t="inlineStr">
+      <c r="C26" s="9" t="inlineStr">
         <is>
           <t>Antoine</t>
         </is>
       </c>
-      <c r="D26" s="10" t="inlineStr">
+      <c r="D26" s="9" t="inlineStr">
         <is>
           <t>Babolat blanche</t>
         </is>
       </c>
-      <c r="E26" s="10" t="inlineStr">
+      <c r="E26" s="9" t="inlineStr">
         <is>
           <t>Asics noir</t>
         </is>
       </c>
-      <c r="F26" s="10" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="4" t="n">
@@ -6739,33 +6196,31 @@
           <t>Unyk noir/gris</t>
         </is>
       </c>
-      <c r="F27" s="6" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="8" t="n">
+      <c r="A28" s="7" t="n">
         <v>24</v>
       </c>
-      <c r="B28" s="9" t="inlineStr">
+      <c r="B28" s="8" t="inlineStr">
         <is>
           <t>TOURRET</t>
         </is>
       </c>
-      <c r="C28" s="10" t="inlineStr">
+      <c r="C28" s="9" t="inlineStr">
         <is>
           <t>Marceau</t>
         </is>
       </c>
-      <c r="D28" s="10" t="inlineStr">
+      <c r="D28" s="9" t="inlineStr">
         <is>
           <t>Hitmark rouge</t>
         </is>
       </c>
-      <c r="E28" s="10" t="inlineStr">
+      <c r="E28" s="9" t="inlineStr">
         <is>
           <t>Hitmark rouge</t>
         </is>
       </c>
-      <c r="F28" s="10" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="4" t="n">
@@ -6791,35 +6246,29 @@
           <t>Nike blanche</t>
         </is>
       </c>
-      <c r="F29" s="6" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="8" t="n">
+      <c r="A30" s="7" t="n">
         <v>26</v>
       </c>
-      <c r="B30" s="9" t="inlineStr">
+      <c r="B30" s="8" t="inlineStr">
         <is>
           <t>VERNY</t>
         </is>
       </c>
-      <c r="C30" s="10" t="inlineStr">
+      <c r="C30" s="9" t="inlineStr">
         <is>
           <t>Antoine</t>
         </is>
       </c>
-      <c r="D30" s="7" t="inlineStr">
+      <c r="D30" s="9" t="inlineStr">
         <is>
           <t>Asics noir</t>
         </is>
       </c>
-      <c r="E30" s="7" t="inlineStr">
+      <c r="E30" s="9" t="inlineStr">
         <is>
           <t>Nike bleu/vert</t>
-        </is>
-      </c>
-      <c r="F30" s="10" t="inlineStr">
-        <is>
-          <t>Inventé : inter + exter</t>
         </is>
       </c>
     </row>
@@ -6847,7 +6296,6 @@
           <t>Nike noir</t>
         </is>
       </c>
-      <c r="F31" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6860,7 +6308,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F32"/>
+  <dimension ref="A1:E32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -6868,7 +6316,6 @@
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="26" customWidth="1" min="4" max="4"/>
     <col width="26" customWidth="1" min="5" max="5"/>
-    <col width="48" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6881,7 +6328,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Case orange = paire inventée (reprise d'une autre paire de la liste)  ·  Case grise = dispensé</t>
+          <t>Case grise = dispensé</t>
         </is>
       </c>
     </row>
@@ -6909,11 +6356,6 @@
       <c r="E4" s="3" t="inlineStr">
         <is>
           <t>Baskets extérieur</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>Remarque</t>
         </is>
       </c>
     </row>
@@ -6941,33 +6383,31 @@
           <t>Asics noir</t>
         </is>
       </c>
-      <c r="F5" s="6" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="8" t="n">
+      <c r="A6" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="9" t="inlineStr">
+      <c r="B6" s="8" t="inlineStr">
         <is>
           <t>BOULLENGER</t>
         </is>
       </c>
-      <c r="C6" s="10" t="inlineStr">
+      <c r="C6" s="9" t="inlineStr">
         <is>
           <t>Rémi</t>
         </is>
       </c>
-      <c r="D6" s="10" t="inlineStr">
+      <c r="D6" s="9" t="inlineStr">
         <is>
           <t>Asics noir</t>
         </is>
       </c>
-      <c r="E6" s="10" t="inlineStr">
+      <c r="E6" s="9" t="inlineStr">
         <is>
           <t>Kalenji bleu</t>
         </is>
       </c>
-      <c r="F6" s="10" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
@@ -6983,49 +6423,39 @@
           <t>Louis</t>
         </is>
       </c>
-      <c r="D7" s="7" t="inlineStr">
+      <c r="D7" s="6" t="inlineStr">
         <is>
           <t>Nike noir</t>
         </is>
       </c>
-      <c r="E7" s="7" t="inlineStr">
+      <c r="E7" s="6" t="inlineStr">
         <is>
           <t>5 Miles bleu</t>
         </is>
       </c>
-      <c r="F7" s="6" t="inlineStr">
-        <is>
-          <t>Inventé : inter + exter</t>
-        </is>
-      </c>
     </row>
     <row r="8">
-      <c r="A8" s="8" t="n">
+      <c r="A8" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="9" t="inlineStr">
+      <c r="B8" s="8" t="inlineStr">
         <is>
           <t>DASSENCOURT</t>
         </is>
       </c>
-      <c r="C8" s="10" t="inlineStr">
+      <c r="C8" s="9" t="inlineStr">
         <is>
           <t>Hugo</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="D8" s="9" t="inlineStr">
         <is>
           <t>Asics noir</t>
         </is>
       </c>
-      <c r="E8" s="7" t="inlineStr">
+      <c r="E8" s="9" t="inlineStr">
         <is>
           <t>Adidas noir</t>
-        </is>
-      </c>
-      <c r="F8" s="10" t="inlineStr">
-        <is>
-          <t>Inventé : inter + exter</t>
         </is>
       </c>
     </row>
@@ -7053,35 +6483,29 @@
           <t>Nike bleu</t>
         </is>
       </c>
-      <c r="F9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="8" t="n">
+      <c r="A10" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="9" t="inlineStr">
+      <c r="B10" s="8" t="inlineStr">
         <is>
           <t>DESSENNE</t>
         </is>
       </c>
-      <c r="C10" s="10" t="inlineStr">
+      <c r="C10" s="9" t="inlineStr">
         <is>
           <t>Cyril</t>
         </is>
       </c>
-      <c r="D10" s="10" t="inlineStr">
+      <c r="D10" s="9" t="inlineStr">
         <is>
           <t>Kalenji gris</t>
         </is>
       </c>
-      <c r="E10" s="7" t="inlineStr">
+      <c r="E10" s="9" t="inlineStr">
         <is>
           <t>Unyk gris/noir</t>
-        </is>
-      </c>
-      <c r="F10" s="10" t="inlineStr">
-        <is>
-          <t>Kalenji : inter/exter non précisé; Inventé : exter</t>
         </is>
       </c>
     </row>
@@ -7109,35 +6533,29 @@
           <t>Kalenji gris</t>
         </is>
       </c>
-      <c r="F11" s="6" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="8" t="n">
+      <c r="A12" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="B12" s="9" t="inlineStr">
+      <c r="B12" s="8" t="inlineStr">
         <is>
           <t>DEUSY</t>
         </is>
       </c>
-      <c r="C12" s="10" t="inlineStr">
+      <c r="C12" s="9" t="inlineStr">
         <is>
           <t>Justin</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="D12" s="9" t="inlineStr">
         <is>
           <t>Adidas noir</t>
         </is>
       </c>
-      <c r="E12" s="10" t="inlineStr">
+      <c r="E12" s="9" t="inlineStr">
         <is>
           <t>Kiprun jaune</t>
-        </is>
-      </c>
-      <c r="F12" s="10" t="inlineStr">
-        <is>
-          <t>Inventé : inter</t>
         </is>
       </c>
     </row>
@@ -7165,33 +6583,31 @@
           <t>Nike noir</t>
         </is>
       </c>
-      <c r="F13" s="6" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="8" t="n">
+      <c r="A14" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="B14" s="9" t="inlineStr">
+      <c r="B14" s="8" t="inlineStr">
         <is>
           <t>DUHAMEL</t>
         </is>
       </c>
-      <c r="C14" s="10" t="inlineStr">
+      <c r="C14" s="9" t="inlineStr">
         <is>
           <t>Louis</t>
         </is>
       </c>
-      <c r="D14" s="10" t="inlineStr">
+      <c r="D14" s="9" t="inlineStr">
         <is>
           <t>Asics bleu/orange</t>
         </is>
       </c>
-      <c r="E14" s="10" t="inlineStr">
+      <c r="E14" s="9" t="inlineStr">
         <is>
           <t>Adidas blanche</t>
         </is>
       </c>
-      <c r="F14" s="10" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
@@ -7217,33 +6633,31 @@
           <t>Nike blanche</t>
         </is>
       </c>
-      <c r="F15" s="6" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="8" t="n">
+      <c r="A16" s="7" t="n">
         <v>12</v>
       </c>
-      <c r="B16" s="9" t="inlineStr">
+      <c r="B16" s="8" t="inlineStr">
         <is>
           <t>GREBERT</t>
         </is>
       </c>
-      <c r="C16" s="10" t="inlineStr">
+      <c r="C16" s="9" t="inlineStr">
         <is>
           <t>Marius</t>
         </is>
       </c>
-      <c r="D16" s="10" t="inlineStr">
+      <c r="D16" s="9" t="inlineStr">
         <is>
           <t>Adidas blanc/violet</t>
         </is>
       </c>
-      <c r="E16" s="10" t="inlineStr">
+      <c r="E16" s="9" t="inlineStr">
         <is>
           <t>NB bleu</t>
         </is>
       </c>
-      <c r="F16" s="10" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="4" t="n">
@@ -7269,33 +6683,31 @@
           <t>Nike beige</t>
         </is>
       </c>
-      <c r="F17" s="6" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="8" t="n">
+      <c r="A18" s="7" t="n">
         <v>14</v>
       </c>
-      <c r="B18" s="9" t="inlineStr">
+      <c r="B18" s="8" t="inlineStr">
         <is>
           <t>HENNEQUIN</t>
         </is>
       </c>
-      <c r="C18" s="10" t="inlineStr">
+      <c r="C18" s="9" t="inlineStr">
         <is>
           <t>Mathis</t>
         </is>
       </c>
-      <c r="D18" s="10" t="inlineStr">
+      <c r="D18" s="9" t="inlineStr">
         <is>
           <t>Nike noir</t>
         </is>
       </c>
-      <c r="E18" s="10" t="inlineStr">
+      <c r="E18" s="9" t="inlineStr">
         <is>
           <t>Nike gris/orange</t>
         </is>
       </c>
-      <c r="F18" s="10" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="4" t="n">
@@ -7321,35 +6733,29 @@
           <t>Hoka bleu</t>
         </is>
       </c>
-      <c r="F19" s="6" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="8" t="n">
+      <c r="A20" s="7" t="n">
         <v>16</v>
       </c>
-      <c r="B20" s="9" t="inlineStr">
+      <c r="B20" s="8" t="inlineStr">
         <is>
           <t>LEFEVRE</t>
         </is>
       </c>
-      <c r="C20" s="10" t="inlineStr">
+      <c r="C20" s="9" t="inlineStr">
         <is>
           <t>Tom</t>
         </is>
       </c>
-      <c r="D20" s="7" t="inlineStr">
+      <c r="D20" s="9" t="inlineStr">
         <is>
           <t>Adidas blanche</t>
         </is>
       </c>
-      <c r="E20" s="7" t="inlineStr">
+      <c r="E20" s="9" t="inlineStr">
         <is>
           <t>Asics gris/jaune</t>
-        </is>
-      </c>
-      <c r="F20" s="10" t="inlineStr">
-        <is>
-          <t>Inventé : inter + exter</t>
         </is>
       </c>
     </row>
@@ -7377,39 +6783,29 @@
           <t>Décathlon gris</t>
         </is>
       </c>
-      <c r="F21" s="6" t="inlineStr">
-        <is>
-          <t>inter/exter non précisé</t>
-        </is>
-      </c>
     </row>
     <row r="22">
-      <c r="A22" s="8" t="n">
+      <c r="A22" s="7" t="n">
         <v>18</v>
       </c>
-      <c r="B22" s="9" t="inlineStr">
+      <c r="B22" s="8" t="inlineStr">
         <is>
           <t>LEPREUX</t>
         </is>
       </c>
-      <c r="C22" s="10" t="inlineStr">
+      <c r="C22" s="9" t="inlineStr">
         <is>
           <t>Théo</t>
         </is>
       </c>
-      <c r="D22" s="7" t="inlineStr">
+      <c r="D22" s="9" t="inlineStr">
         <is>
           <t>Nike noir</t>
         </is>
       </c>
-      <c r="E22" s="7" t="inlineStr">
+      <c r="E22" s="9" t="inlineStr">
         <is>
           <t>Nike noir</t>
-        </is>
-      </c>
-      <c r="F22" s="10" t="inlineStr">
-        <is>
-          <t>Inventé : inter + exter</t>
         </is>
       </c>
     </row>
@@ -7437,35 +6833,29 @@
           <t>Décathlon gris</t>
         </is>
       </c>
-      <c r="F23" s="6" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="8" t="n">
+      <c r="A24" s="7" t="n">
         <v>20</v>
       </c>
-      <c r="B24" s="9" t="inlineStr">
+      <c r="B24" s="8" t="inlineStr">
         <is>
           <t>MONTIER</t>
         </is>
       </c>
-      <c r="C24" s="10" t="inlineStr">
+      <c r="C24" s="9" t="inlineStr">
         <is>
           <t>Nathan</t>
         </is>
       </c>
-      <c r="D24" s="10" t="inlineStr">
+      <c r="D24" s="9" t="inlineStr">
         <is>
           <t>Nike blanche</t>
         </is>
       </c>
-      <c r="E24" s="7" t="inlineStr">
+      <c r="E24" s="9" t="inlineStr">
         <is>
           <t>Nike noir</t>
-        </is>
-      </c>
-      <c r="F24" s="10" t="inlineStr">
-        <is>
-          <t>Inventé : exter</t>
         </is>
       </c>
     </row>
@@ -7493,33 +6883,31 @@
           <t>Kalenji bleu</t>
         </is>
       </c>
-      <c r="F25" s="6" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="8" t="n">
+      <c r="A26" s="7" t="n">
         <v>22</v>
       </c>
-      <c r="B26" s="9" t="inlineStr">
+      <c r="B26" s="8" t="inlineStr">
         <is>
           <t>PRUVOST</t>
         </is>
       </c>
-      <c r="C26" s="10" t="inlineStr">
+      <c r="C26" s="9" t="inlineStr">
         <is>
           <t>Maxence</t>
         </is>
       </c>
-      <c r="D26" s="10" t="inlineStr">
+      <c r="D26" s="9" t="inlineStr">
         <is>
           <t>Nike noir</t>
         </is>
       </c>
-      <c r="E26" s="10" t="inlineStr">
+      <c r="E26" s="9" t="inlineStr">
         <is>
           <t>Kalenji noir/vert</t>
         </is>
       </c>
-      <c r="F26" s="10" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="4" t="n">
@@ -7545,33 +6933,31 @@
           <t>Nike noir/rouge</t>
         </is>
       </c>
-      <c r="F27" s="6" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="8" t="n">
+      <c r="A28" s="7" t="n">
         <v>24</v>
       </c>
-      <c r="B28" s="9" t="inlineStr">
+      <c r="B28" s="8" t="inlineStr">
         <is>
           <t>SAMAIN</t>
         </is>
       </c>
-      <c r="C28" s="10" t="inlineStr">
+      <c r="C28" s="9" t="inlineStr">
         <is>
           <t>Baptiste</t>
         </is>
       </c>
-      <c r="D28" s="10" t="inlineStr">
+      <c r="D28" s="9" t="inlineStr">
         <is>
           <t>Kalenji gris</t>
         </is>
       </c>
-      <c r="E28" s="10" t="inlineStr">
+      <c r="E28" s="9" t="inlineStr">
         <is>
           <t>Asics bleu</t>
         </is>
       </c>
-      <c r="F28" s="10" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="4" t="n">
@@ -7597,33 +6983,31 @@
           <t>Asics bleu</t>
         </is>
       </c>
-      <c r="F29" s="6" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="8" t="n">
+      <c r="A30" s="7" t="n">
         <v>26</v>
       </c>
-      <c r="B30" s="9" t="inlineStr">
+      <c r="B30" s="8" t="inlineStr">
         <is>
           <t>THUILLET</t>
         </is>
       </c>
-      <c r="C30" s="10" t="inlineStr">
+      <c r="C30" s="9" t="inlineStr">
         <is>
           <t>Ethan</t>
         </is>
       </c>
-      <c r="D30" s="10" t="inlineStr">
+      <c r="D30" s="9" t="inlineStr">
         <is>
           <t>Décathlon gris</t>
         </is>
       </c>
-      <c r="E30" s="10" t="inlineStr">
+      <c r="E30" s="9" t="inlineStr">
         <is>
           <t>Décathlon noir</t>
         </is>
       </c>
-      <c r="F30" s="10" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="4" t="n">
@@ -7649,33 +7033,31 @@
           <t>Nike noir/blanc</t>
         </is>
       </c>
-      <c r="F31" s="6" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="8" t="n">
+      <c r="A32" s="7" t="n">
         <v>28</v>
       </c>
-      <c r="B32" s="9" t="inlineStr">
+      <c r="B32" s="8" t="inlineStr">
         <is>
           <t>YZANIC</t>
         </is>
       </c>
-      <c r="C32" s="10" t="inlineStr">
+      <c r="C32" s="9" t="inlineStr">
         <is>
           <t>Erwan</t>
         </is>
       </c>
-      <c r="D32" s="10" t="inlineStr">
+      <c r="D32" s="9" t="inlineStr">
         <is>
           <t>NB blanc/gris</t>
         </is>
       </c>
-      <c r="E32" s="10" t="inlineStr">
+      <c r="E32" s="9" t="inlineStr">
         <is>
           <t>Adidas bleu marine</t>
         </is>
       </c>
-      <c r="F32" s="10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
